--- a/datos/distribucion/req_precio/2026-05/REQ_05_2026_PRECIO_6.50.xlsx
+++ b/datos/distribucion/req_precio/2026-05/REQ_05_2026_PRECIO_6.50.xlsx
@@ -49593,7 +49593,7 @@
   <sheetPr codeName="Hoja2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q649"/>
+  <dimension ref="A1:Q654"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="7" customWidth="1"/>
@@ -66747,19 +66747,19 @@
     </row>
     <row r="549">
       <c r="A549" s="1">
-        <v>324118</v>
+        <v>67143</v>
       </c>
       <c r="B549" s="52"/>
       <c r="C549" s="53" t="inlineStr">
         <is>
-          <t>SAN MIGUEL FIGUEROA</t>
+          <t>LA JOYA</t>
         </is>
       </c>
       <c r="D549" s="57">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="E549" s="57">
-        <v>111</v>
+        <v>240</v>
       </c>
       <c r="F549" s="10">
         <f>E549*0.666*24/72</f>
@@ -66796,3350 +66796,3340 @@
         <f>+P549</f>
       </c>
     </row>
+    <row r="550">
+      <c r="A550" s="1">
+        <v>72104</v>
+      </c>
+      <c r="B550" s="52"/>
+      <c r="C550" s="53" t="inlineStr">
+        <is>
+          <t>SAN JOSE DEL PROGRESO</t>
+        </is>
+      </c>
+      <c r="D550" s="57">
+        <v>150</v>
+      </c>
+      <c r="E550" s="57">
+        <v>280</v>
+      </c>
+      <c r="F550" s="10">
+        <f>E550*0.666*24/72</f>
+      </c>
+      <c r="G550" s="54">
+        <v>0</v>
+      </c>
+      <c r="H550" s="54">
+        <v>0</v>
+      </c>
+      <c r="I550" s="54">
+        <v>0</v>
+      </c>
+      <c r="J550" s="54">
+        <v>0</v>
+      </c>
+      <c r="K550" s="54">
+        <v>0</v>
+      </c>
+      <c r="L550" s="55">
+        <v>0</v>
+      </c>
+      <c r="M550" s="54">
+        <v>0</v>
+      </c>
+      <c r="N550" s="55">
+        <v>0</v>
+      </c>
+      <c r="O550" s="10">
+        <v>0</v>
+      </c>
+      <c r="P550" s="54"/>
+      <c r="Q550" s="56">
+        <f>+P550</f>
+      </c>
+    </row>
     <row r="551">
-      <c r="A551" s="43" t="inlineStr">
+      <c r="A551" s="1">
+        <v>115104</v>
+      </c>
+      <c r="B551" s="52"/>
+      <c r="C551" s="53" t="inlineStr">
+        <is>
+          <t>REYES MANTECON</t>
+        </is>
+      </c>
+      <c r="D551" s="57">
+        <v>182</v>
+      </c>
+      <c r="E551" s="57">
+        <v>388</v>
+      </c>
+      <c r="F551" s="10">
+        <f>E551*0.666*24/72</f>
+      </c>
+      <c r="G551" s="54">
+        <v>0</v>
+      </c>
+      <c r="H551" s="54">
+        <v>0</v>
+      </c>
+      <c r="I551" s="54">
+        <v>0</v>
+      </c>
+      <c r="J551" s="54">
+        <v>0</v>
+      </c>
+      <c r="K551" s="54">
+        <v>0</v>
+      </c>
+      <c r="L551" s="55">
+        <v>0</v>
+      </c>
+      <c r="M551" s="54">
+        <v>0</v>
+      </c>
+      <c r="N551" s="55">
+        <v>0</v>
+      </c>
+      <c r="O551" s="10">
+        <v>0</v>
+      </c>
+      <c r="P551" s="54"/>
+      <c r="Q551" s="56">
+        <f>+P551</f>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1">
+        <v>324118</v>
+      </c>
+      <c r="B552" s="52"/>
+      <c r="C552" s="53" t="inlineStr">
+        <is>
+          <t>SAN MIGUEL FIGUEROA</t>
+        </is>
+      </c>
+      <c r="D552" s="57">
+        <v>73</v>
+      </c>
+      <c r="E552" s="57">
+        <v>111</v>
+      </c>
+      <c r="F552" s="10">
+        <f>E552*0.666*24/72</f>
+      </c>
+      <c r="G552" s="54">
+        <v>0</v>
+      </c>
+      <c r="H552" s="54">
+        <v>0</v>
+      </c>
+      <c r="I552" s="54">
+        <v>0</v>
+      </c>
+      <c r="J552" s="54">
+        <v>0</v>
+      </c>
+      <c r="K552" s="54">
+        <v>0</v>
+      </c>
+      <c r="L552" s="55">
+        <v>0</v>
+      </c>
+      <c r="M552" s="54">
+        <v>0</v>
+      </c>
+      <c r="N552" s="55">
+        <v>0</v>
+      </c>
+      <c r="O552" s="10">
+        <v>0</v>
+      </c>
+      <c r="P552" s="54"/>
+      <c r="Q552" s="56">
+        <f>+P552</f>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1">
+        <v>399111</v>
+      </c>
+      <c r="B553" s="52"/>
+      <c r="C553" s="53" t="inlineStr">
+        <is>
+          <t>REAL SANTA MARIA FRACCIONAMIENTO</t>
+        </is>
+      </c>
+      <c r="D553" s="57">
+        <v>126</v>
+      </c>
+      <c r="E553" s="57">
+        <v>232</v>
+      </c>
+      <c r="F553" s="10">
+        <f>E553*0.666*24/72</f>
+      </c>
+      <c r="G553" s="54">
+        <v>0</v>
+      </c>
+      <c r="H553" s="54">
+        <v>0</v>
+      </c>
+      <c r="I553" s="54">
+        <v>0</v>
+      </c>
+      <c r="J553" s="54">
+        <v>0</v>
+      </c>
+      <c r="K553" s="54">
+        <v>0</v>
+      </c>
+      <c r="L553" s="55">
+        <v>0</v>
+      </c>
+      <c r="M553" s="54">
+        <v>0</v>
+      </c>
+      <c r="N553" s="55">
+        <v>0</v>
+      </c>
+      <c r="O553" s="10">
+        <v>0</v>
+      </c>
+      <c r="P553" s="54"/>
+      <c r="Q553" s="56">
+        <f>+P553</f>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1">
+        <v>565117</v>
+      </c>
+      <c r="B554" s="52"/>
+      <c r="C554" s="53" t="inlineStr">
+        <is>
+          <t>BENITO JUAREZ</t>
+        </is>
+      </c>
+      <c r="D554" s="57">
+        <v>103</v>
+      </c>
+      <c r="E554" s="57">
+        <v>217</v>
+      </c>
+      <c r="F554" s="10">
+        <f>E554*0.666*24/72</f>
+      </c>
+      <c r="G554" s="54">
+        <v>0</v>
+      </c>
+      <c r="H554" s="54">
+        <v>0</v>
+      </c>
+      <c r="I554" s="54">
+        <v>0</v>
+      </c>
+      <c r="J554" s="54">
+        <v>0</v>
+      </c>
+      <c r="K554" s="54">
+        <v>0</v>
+      </c>
+      <c r="L554" s="55">
+        <v>0</v>
+      </c>
+      <c r="M554" s="54">
+        <v>0</v>
+      </c>
+      <c r="N554" s="55">
+        <v>0</v>
+      </c>
+      <c r="O554" s="10">
+        <v>0</v>
+      </c>
+      <c r="P554" s="54"/>
+      <c r="Q554" s="56">
+        <f>+P554</f>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="43" t="inlineStr">
         <is>
           <t>T O T A L</t>
         </is>
       </c>
-      <c r="B551" s="44"/>
-      <c r="C551" s="45">
-        <f>COUNTA(A549:A549)</f>
-      </c>
-      <c r="D551" s="65">
-        <f>SUM(D549:D549)</f>
-      </c>
-      <c r="E551" s="65">
-        <f>SUM(E549:E549)</f>
-      </c>
-      <c r="F551" s="65">
-        <f>SUM(F549:F549)</f>
-      </c>
-      <c r="G551" s="65">
-        <f>SUM(G549:G549)</f>
-      </c>
-      <c r="H551" s="65">
-        <f>SUM(H549:H549)</f>
-      </c>
-      <c r="I551" s="65">
-        <f>SUM(I549:I549)</f>
-      </c>
-      <c r="J551" s="65">
-        <f>SUM(J549:J549)</f>
-      </c>
-      <c r="K551" s="65">
-        <f>SUM(K549:K549)</f>
-      </c>
-      <c r="L551" s="65">
-        <f>SUM(L549:L549)</f>
-      </c>
-      <c r="M551" s="65">
-        <f>SUM(M549:M549)</f>
-      </c>
-      <c r="N551" s="65">
-        <f>SUM(N549:N549)</f>
-      </c>
-      <c r="O551" s="65">
-        <f>SUM(O549:O549)</f>
-      </c>
-      <c r="P551" s="65">
-        <f>SUM(P549:P549)</f>
-      </c>
-      <c r="Q551" s="65">
-        <f>SUM(Q549:Q549)</f>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" s="66" t="inlineStr">
+      <c r="B556" s="44"/>
+      <c r="C556" s="45">
+        <f>COUNTA(A549:A554)</f>
+      </c>
+      <c r="D556" s="65">
+        <f>SUM(D549:D554)</f>
+      </c>
+      <c r="E556" s="65">
+        <f>SUM(E549:E554)</f>
+      </c>
+      <c r="F556" s="65">
+        <f>SUM(F549:F554)</f>
+      </c>
+      <c r="G556" s="65">
+        <f>SUM(G549:G554)</f>
+      </c>
+      <c r="H556" s="65">
+        <f>SUM(H549:H554)</f>
+      </c>
+      <c r="I556" s="65">
+        <f>SUM(I549:I554)</f>
+      </c>
+      <c r="J556" s="65">
+        <f>SUM(J549:J554)</f>
+      </c>
+      <c r="K556" s="65">
+        <f>SUM(K549:K554)</f>
+      </c>
+      <c r="L556" s="65">
+        <f>SUM(L549:L554)</f>
+      </c>
+      <c r="M556" s="65">
+        <f>SUM(M549:M554)</f>
+      </c>
+      <c r="N556" s="65">
+        <f>SUM(N549:N554)</f>
+      </c>
+      <c r="O556" s="65">
+        <f>SUM(O549:O554)</f>
+      </c>
+      <c r="P556" s="65">
+        <f>SUM(P549:P554)</f>
+      </c>
+      <c r="Q556" s="65">
+        <f>SUM(Q549:Q554)</f>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="66" t="inlineStr">
         <is>
           <t>OBSERVACIONES: </t>
         </is>
       </c>
-      <c r="B552" s="67"/>
-      <c r="C552" s="68"/>
-      <c r="D552" s="69"/>
-      <c r="E552" s="69"/>
-      <c r="F552" s="70"/>
-      <c r="G552" s="69"/>
-      <c r="H552" s="69"/>
-      <c r="I552" s="69"/>
-      <c r="J552" s="69"/>
-      <c r="K552" s="69"/>
-      <c r="L552" s="70"/>
-      <c r="M552" s="71"/>
-      <c r="N552" s="72"/>
-      <c r="O552" s="72"/>
-      <c r="P552" s="73"/>
-      <c r="Q552" s="74"/>
-    </row>
-    <row r="553">
-      <c r="P553" s="65" t="inlineStr">
+      <c r="B557" s="67"/>
+      <c r="C557" s="68"/>
+      <c r="D557" s="69"/>
+      <c r="E557" s="69"/>
+      <c r="F557" s="70"/>
+      <c r="G557" s="69"/>
+      <c r="H557" s="69"/>
+      <c r="I557" s="69"/>
+      <c r="J557" s="69"/>
+      <c r="K557" s="69"/>
+      <c r="L557" s="70"/>
+      <c r="M557" s="71"/>
+      <c r="N557" s="72"/>
+      <c r="O557" s="72"/>
+      <c r="P557" s="73"/>
+      <c r="Q557" s="74"/>
+    </row>
+    <row r="558">
+      <c r="P558" s="65" t="inlineStr">
         <is>
           <t>TOTAL A RECIBIR EN ALMACEN:</t>
         </is>
       </c>
-      <c r="Q553" s="65">
-        <f>Q551</f>
-      </c>
-    </row>
-    <row r="556">
-      <c r="B556" s="40" t="inlineStr">
+      <c r="Q558" s="65">
+        <f>Q556</f>
+      </c>
+    </row>
+    <row r="561">
+      <c r="B561" s="40" t="inlineStr">
         <is>
           <t>ALMACEN RURAL : GUADALUPE ETLA</t>
         </is>
       </c>
-      <c r="C556" s="41"/>
-    </row>
-    <row r="559">
-      <c r="A559" s="1">
+      <c r="C561" s="41"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="1">
         <v>2104</v>
       </c>
-      <c r="B559" s="52">
+      <c r="B564" s="52">
         <v>10101</v>
       </c>
-      <c r="C559" s="53" t="inlineStr">
+      <c r="C564" s="53" t="inlineStr">
         <is>
           <t>ZONA URBANA</t>
         </is>
       </c>
-      <c r="D559" s="57">
+      <c r="D564" s="57">
         <v>88</v>
       </c>
-      <c r="E559" s="57">
+      <c r="E564" s="57">
         <v>128</v>
       </c>
-      <c r="F559" s="10">
-        <f>E559*0.666*24/72</f>
-      </c>
-      <c r="G559" s="54">
-        <v>0</v>
-      </c>
-      <c r="H559" s="54">
-        <v>0</v>
-      </c>
-      <c r="I559" s="54">
-        <v>0</v>
-      </c>
-      <c r="J559" s="54">
-        <v>0</v>
-      </c>
-      <c r="K559" s="54">
-        <v>0</v>
-      </c>
-      <c r="L559" s="55">
-        <v>0</v>
-      </c>
-      <c r="M559" s="54">
-        <v>0</v>
-      </c>
-      <c r="N559" s="55">
-        <v>0</v>
-      </c>
-      <c r="O559" s="10">
-        <v>0</v>
-      </c>
-      <c r="P559" s="54"/>
-      <c r="Q559" s="56">
-        <f>+P559</f>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" s="1">
+      <c r="F564" s="10">
+        <f>E564*0.666*24/72</f>
+      </c>
+      <c r="G564" s="54">
+        <v>0</v>
+      </c>
+      <c r="H564" s="54">
+        <v>0</v>
+      </c>
+      <c r="I564" s="54">
+        <v>0</v>
+      </c>
+      <c r="J564" s="54">
+        <v>0</v>
+      </c>
+      <c r="K564" s="54">
+        <v>0</v>
+      </c>
+      <c r="L564" s="55">
+        <v>0</v>
+      </c>
+      <c r="M564" s="54">
+        <v>0</v>
+      </c>
+      <c r="N564" s="55">
+        <v>0</v>
+      </c>
+      <c r="O564" s="10">
+        <v>0</v>
+      </c>
+      <c r="P564" s="54"/>
+      <c r="Q564" s="56">
+        <f>+P564</f>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1">
         <v>2105</v>
       </c>
-      <c r="B560" s="52">
+      <c r="B565" s="52">
         <v>10101</v>
       </c>
-      <c r="C560" s="53" t="inlineStr">
+      <c r="C565" s="53" t="inlineStr">
         <is>
           <t>ACATLAN DE PEREZ FIGUEROA</t>
         </is>
       </c>
-      <c r="D560" s="57">
+      <c r="D565" s="57">
         <v>221</v>
       </c>
-      <c r="E560" s="57">
+      <c r="E565" s="57">
         <v>360</v>
       </c>
-      <c r="F560" s="10">
-        <f>E560*0.666*24/72</f>
-      </c>
-      <c r="G560" s="54">
-        <v>0</v>
-      </c>
-      <c r="H560" s="54">
-        <v>0</v>
-      </c>
-      <c r="I560" s="54">
-        <v>0</v>
-      </c>
-      <c r="J560" s="54">
-        <v>0</v>
-      </c>
-      <c r="K560" s="54">
-        <v>0</v>
-      </c>
-      <c r="L560" s="55">
-        <v>0</v>
-      </c>
-      <c r="M560" s="54">
-        <v>0</v>
-      </c>
-      <c r="N560" s="55">
-        <v>0</v>
-      </c>
-      <c r="O560" s="10">
-        <v>0</v>
-      </c>
-      <c r="P560" s="54"/>
-      <c r="Q560" s="56">
-        <f>+P560</f>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" s="1">
+      <c r="F565" s="10">
+        <f>E565*0.666*24/72</f>
+      </c>
+      <c r="G565" s="54">
+        <v>0</v>
+      </c>
+      <c r="H565" s="54">
+        <v>0</v>
+      </c>
+      <c r="I565" s="54">
+        <v>0</v>
+      </c>
+      <c r="J565" s="54">
+        <v>0</v>
+      </c>
+      <c r="K565" s="54">
+        <v>0</v>
+      </c>
+      <c r="L565" s="55">
+        <v>0</v>
+      </c>
+      <c r="M565" s="54">
+        <v>0</v>
+      </c>
+      <c r="N565" s="55">
+        <v>0</v>
+      </c>
+      <c r="O565" s="10">
+        <v>0</v>
+      </c>
+      <c r="P565" s="54"/>
+      <c r="Q565" s="56">
+        <f>+P565</f>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1">
         <v>2106</v>
       </c>
-      <c r="B561" s="52">
+      <c r="B566" s="52">
         <v>10101</v>
       </c>
-      <c r="C561" s="53" t="inlineStr">
+      <c r="C566" s="53" t="inlineStr">
         <is>
           <t>VICENTE CAMALOTE</t>
         </is>
       </c>
-      <c r="D561" s="57">
+      <c r="D566" s="57">
         <v>123</v>
       </c>
-      <c r="E561" s="57">
+      <c r="E566" s="57">
         <v>201</v>
       </c>
-      <c r="F561" s="10">
-        <f>E561*0.666*24/72</f>
-      </c>
-      <c r="G561" s="54">
-        <v>0</v>
-      </c>
-      <c r="H561" s="54">
-        <v>0</v>
-      </c>
-      <c r="I561" s="54">
-        <v>0</v>
-      </c>
-      <c r="J561" s="54">
-        <v>0</v>
-      </c>
-      <c r="K561" s="54">
-        <v>0</v>
-      </c>
-      <c r="L561" s="55">
-        <v>0</v>
-      </c>
-      <c r="M561" s="54">
-        <v>0</v>
-      </c>
-      <c r="N561" s="55">
-        <v>0</v>
-      </c>
-      <c r="O561" s="10">
-        <v>0</v>
-      </c>
-      <c r="P561" s="54"/>
-      <c r="Q561" s="56">
-        <f>+P561</f>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" s="1">
+      <c r="F566" s="10">
+        <f>E566*0.666*24/72</f>
+      </c>
+      <c r="G566" s="54">
+        <v>0</v>
+      </c>
+      <c r="H566" s="54">
+        <v>0</v>
+      </c>
+      <c r="I566" s="54">
+        <v>0</v>
+      </c>
+      <c r="J566" s="54">
+        <v>0</v>
+      </c>
+      <c r="K566" s="54">
+        <v>0</v>
+      </c>
+      <c r="L566" s="55">
+        <v>0</v>
+      </c>
+      <c r="M566" s="54">
+        <v>0</v>
+      </c>
+      <c r="N566" s="55">
+        <v>0</v>
+      </c>
+      <c r="O566" s="10">
+        <v>0</v>
+      </c>
+      <c r="P566" s="54"/>
+      <c r="Q566" s="56">
+        <f>+P566</f>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1">
         <v>6103</v>
       </c>
-      <c r="B562" s="52">
+      <c r="B567" s="52">
         <v>10101</v>
       </c>
-      <c r="C562" s="53" t="inlineStr">
+      <c r="C567" s="53" t="inlineStr">
         <is>
           <t>AMPLIACION CHOCANO</t>
         </is>
       </c>
-      <c r="D562" s="57">
+      <c r="D567" s="57">
         <v>224</v>
       </c>
-      <c r="E562" s="57">
+      <c r="E567" s="57">
         <v>331</v>
       </c>
-      <c r="F562" s="10">
-        <f>E562*0.666*24/72</f>
-      </c>
-      <c r="G562" s="54">
-        <v>0</v>
-      </c>
-      <c r="H562" s="54">
-        <v>0</v>
-      </c>
-      <c r="I562" s="54">
-        <v>0</v>
-      </c>
-      <c r="J562" s="54">
-        <v>0</v>
-      </c>
-      <c r="K562" s="54">
-        <v>0</v>
-      </c>
-      <c r="L562" s="55">
-        <v>0</v>
-      </c>
-      <c r="M562" s="54">
-        <v>0</v>
-      </c>
-      <c r="N562" s="55">
-        <v>0</v>
-      </c>
-      <c r="O562" s="10">
-        <v>0</v>
-      </c>
-      <c r="P562" s="54"/>
-      <c r="Q562" s="56">
-        <f>+P562</f>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" s="1">
+      <c r="F567" s="10">
+        <f>E567*0.666*24/72</f>
+      </c>
+      <c r="G567" s="54">
+        <v>0</v>
+      </c>
+      <c r="H567" s="54">
+        <v>0</v>
+      </c>
+      <c r="I567" s="54">
+        <v>0</v>
+      </c>
+      <c r="J567" s="54">
+        <v>0</v>
+      </c>
+      <c r="K567" s="54">
+        <v>0</v>
+      </c>
+      <c r="L567" s="55">
+        <v>0</v>
+      </c>
+      <c r="M567" s="54">
+        <v>0</v>
+      </c>
+      <c r="N567" s="55">
+        <v>0</v>
+      </c>
+      <c r="O567" s="10">
+        <v>0</v>
+      </c>
+      <c r="P567" s="54"/>
+      <c r="Q567" s="56">
+        <f>+P567</f>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1">
         <v>6104</v>
       </c>
-      <c r="B563" s="52">
+      <c r="B568" s="52">
         <v>10101</v>
       </c>
-      <c r="C563" s="53" t="inlineStr">
+      <c r="C568" s="53" t="inlineStr">
         <is>
           <t>ASUNCION NOCHIXTLAN EL CALVARIO</t>
         </is>
       </c>
-      <c r="D563" s="57">
+      <c r="D568" s="57">
         <v>582</v>
       </c>
-      <c r="E563" s="57">
+      <c r="E568" s="57">
         <v>943</v>
       </c>
-      <c r="F563" s="10">
-        <f>E563*0.666*24/72</f>
-      </c>
-      <c r="G563" s="54">
-        <v>0</v>
-      </c>
-      <c r="H563" s="54">
-        <v>0</v>
-      </c>
-      <c r="I563" s="54">
-        <v>0</v>
-      </c>
-      <c r="J563" s="54">
-        <v>0</v>
-      </c>
-      <c r="K563" s="54">
-        <v>0</v>
-      </c>
-      <c r="L563" s="55">
-        <v>0</v>
-      </c>
-      <c r="M563" s="54">
-        <v>0</v>
-      </c>
-      <c r="N563" s="55">
-        <v>0</v>
-      </c>
-      <c r="O563" s="10">
-        <v>0</v>
-      </c>
-      <c r="P563" s="54"/>
-      <c r="Q563" s="56">
-        <f>+P563</f>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" s="1">
+      <c r="F568" s="10">
+        <f>E568*0.666*24/72</f>
+      </c>
+      <c r="G568" s="54">
+        <v>0</v>
+      </c>
+      <c r="H568" s="54">
+        <v>0</v>
+      </c>
+      <c r="I568" s="54">
+        <v>0</v>
+      </c>
+      <c r="J568" s="54">
+        <v>0</v>
+      </c>
+      <c r="K568" s="54">
+        <v>0</v>
+      </c>
+      <c r="L568" s="55">
+        <v>0</v>
+      </c>
+      <c r="M568" s="54">
+        <v>0</v>
+      </c>
+      <c r="N568" s="55">
+        <v>0</v>
+      </c>
+      <c r="O568" s="10">
+        <v>0</v>
+      </c>
+      <c r="P568" s="54"/>
+      <c r="Q568" s="56">
+        <f>+P568</f>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1">
         <v>10101</v>
       </c>
-      <c r="B564" s="52">
+      <c r="B569" s="52">
         <v>10101</v>
       </c>
-      <c r="C564" s="53" t="inlineStr">
+      <c r="C569" s="53" t="inlineStr">
         <is>
           <t>BARRIO LA SOLEDAD</t>
         </is>
       </c>
-      <c r="D564" s="57">
+      <c r="D569" s="57">
         <v>183</v>
       </c>
-      <c r="E564" s="57">
+      <c r="E569" s="57">
         <v>292</v>
       </c>
-      <c r="F564" s="10">
-        <f>E564*0.666*24/72</f>
-      </c>
-      <c r="G564" s="54">
-        <v>0</v>
-      </c>
-      <c r="H564" s="54">
-        <v>0</v>
-      </c>
-      <c r="I564" s="54">
-        <v>0</v>
-      </c>
-      <c r="J564" s="54">
-        <v>0</v>
-      </c>
-      <c r="K564" s="54">
-        <v>0</v>
-      </c>
-      <c r="L564" s="55">
-        <v>0</v>
-      </c>
-      <c r="M564" s="54">
-        <v>0</v>
-      </c>
-      <c r="N564" s="55">
-        <v>0</v>
-      </c>
-      <c r="O564" s="10">
-        <v>0</v>
-      </c>
-      <c r="P564" s="54"/>
-      <c r="Q564" s="56">
-        <f>+P564</f>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" s="1">
+      <c r="F569" s="10">
+        <f>E569*0.666*24/72</f>
+      </c>
+      <c r="G569" s="54">
+        <v>0</v>
+      </c>
+      <c r="H569" s="54">
+        <v>0</v>
+      </c>
+      <c r="I569" s="54">
+        <v>0</v>
+      </c>
+      <c r="J569" s="54">
+        <v>0</v>
+      </c>
+      <c r="K569" s="54">
+        <v>0</v>
+      </c>
+      <c r="L569" s="55">
+        <v>0</v>
+      </c>
+      <c r="M569" s="54">
+        <v>0</v>
+      </c>
+      <c r="N569" s="55">
+        <v>0</v>
+      </c>
+      <c r="O569" s="10">
+        <v>0</v>
+      </c>
+      <c r="P569" s="54"/>
+      <c r="Q569" s="56">
+        <f>+P569</f>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1">
         <v>14104</v>
       </c>
-      <c r="B565" s="52">
+      <c r="B570" s="52">
         <v>10101</v>
       </c>
-      <c r="C565" s="53" t="inlineStr">
+      <c r="C570" s="53" t="inlineStr">
         <is>
           <t>CIUDAD IXTEPEC</t>
         </is>
       </c>
-      <c r="D565" s="57">
+      <c r="D570" s="57">
         <v>285</v>
       </c>
-      <c r="E565" s="57">
+      <c r="E570" s="57">
         <v>425</v>
       </c>
-      <c r="F565" s="10">
-        <f>E565*0.666*24/72</f>
-      </c>
-      <c r="G565" s="54">
-        <v>0</v>
-      </c>
-      <c r="H565" s="54">
-        <v>0</v>
-      </c>
-      <c r="I565" s="54">
-        <v>0</v>
-      </c>
-      <c r="J565" s="54">
-        <v>0</v>
-      </c>
-      <c r="K565" s="54">
-        <v>0</v>
-      </c>
-      <c r="L565" s="55">
-        <v>0</v>
-      </c>
-      <c r="M565" s="54">
-        <v>0</v>
-      </c>
-      <c r="N565" s="55">
-        <v>0</v>
-      </c>
-      <c r="O565" s="10">
-        <v>0</v>
-      </c>
-      <c r="P565" s="54"/>
-      <c r="Q565" s="56">
-        <f>+P565</f>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" s="1">
+      <c r="F570" s="10">
+        <f>E570*0.666*24/72</f>
+      </c>
+      <c r="G570" s="54">
+        <v>0</v>
+      </c>
+      <c r="H570" s="54">
+        <v>0</v>
+      </c>
+      <c r="I570" s="54">
+        <v>0</v>
+      </c>
+      <c r="J570" s="54">
+        <v>0</v>
+      </c>
+      <c r="K570" s="54">
+        <v>0</v>
+      </c>
+      <c r="L570" s="55">
+        <v>0</v>
+      </c>
+      <c r="M570" s="54">
+        <v>0</v>
+      </c>
+      <c r="N570" s="55">
+        <v>0</v>
+      </c>
+      <c r="O570" s="10">
+        <v>0</v>
+      </c>
+      <c r="P570" s="54"/>
+      <c r="Q570" s="56">
+        <f>+P570</f>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1">
         <v>30102</v>
       </c>
-      <c r="B566" s="52">
+      <c r="B571" s="52">
         <v>10101</v>
       </c>
-      <c r="C566" s="53" t="inlineStr">
+      <c r="C571" s="53" t="inlineStr">
         <is>
           <t>EL ESPINAL</t>
         </is>
       </c>
-      <c r="D566" s="57">
+      <c r="D571" s="57">
         <v>84</v>
       </c>
-      <c r="E566" s="57">
+      <c r="E571" s="57">
         <v>125</v>
       </c>
-      <c r="F566" s="10">
-        <f>E566*0.666*24/72</f>
-      </c>
-      <c r="G566" s="54">
-        <v>0</v>
-      </c>
-      <c r="H566" s="54">
-        <v>0</v>
-      </c>
-      <c r="I566" s="54">
-        <v>0</v>
-      </c>
-      <c r="J566" s="54">
-        <v>0</v>
-      </c>
-      <c r="K566" s="54">
-        <v>0</v>
-      </c>
-      <c r="L566" s="55">
-        <v>0</v>
-      </c>
-      <c r="M566" s="54">
-        <v>0</v>
-      </c>
-      <c r="N566" s="55">
-        <v>0</v>
-      </c>
-      <c r="O566" s="10">
-        <v>0</v>
-      </c>
-      <c r="P566" s="54"/>
-      <c r="Q566" s="56">
-        <f>+P566</f>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" s="1">
+      <c r="F571" s="10">
+        <f>E571*0.666*24/72</f>
+      </c>
+      <c r="G571" s="54">
+        <v>0</v>
+      </c>
+      <c r="H571" s="54">
+        <v>0</v>
+      </c>
+      <c r="I571" s="54">
+        <v>0</v>
+      </c>
+      <c r="J571" s="54">
+        <v>0</v>
+      </c>
+      <c r="K571" s="54">
+        <v>0</v>
+      </c>
+      <c r="L571" s="55">
+        <v>0</v>
+      </c>
+      <c r="M571" s="54">
+        <v>0</v>
+      </c>
+      <c r="N571" s="55">
+        <v>0</v>
+      </c>
+      <c r="O571" s="10">
+        <v>0</v>
+      </c>
+      <c r="P571" s="54"/>
+      <c r="Q571" s="56">
+        <f>+P571</f>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1">
         <v>39102</v>
       </c>
-      <c r="B567" s="52">
+      <c r="B572" s="52">
         <v>10101</v>
       </c>
-      <c r="C567" s="53" t="inlineStr">
+      <c r="C572" s="53" t="inlineStr">
         <is>
           <t>COL  CENTRO</t>
         </is>
       </c>
-      <c r="D567" s="57">
+      <c r="D572" s="57">
         <v>440</v>
       </c>
-      <c r="E567" s="57">
+      <c r="E572" s="57">
         <v>708</v>
       </c>
-      <c r="F567" s="10">
-        <f>E567*0.666*24/72</f>
-      </c>
-      <c r="G567" s="54">
-        <v>0</v>
-      </c>
-      <c r="H567" s="54">
-        <v>0</v>
-      </c>
-      <c r="I567" s="54">
-        <v>0</v>
-      </c>
-      <c r="J567" s="54">
-        <v>0</v>
-      </c>
-      <c r="K567" s="54">
-        <v>0</v>
-      </c>
-      <c r="L567" s="55">
-        <v>0</v>
-      </c>
-      <c r="M567" s="54">
-        <v>0</v>
-      </c>
-      <c r="N567" s="55">
-        <v>0</v>
-      </c>
-      <c r="O567" s="10">
-        <v>0</v>
-      </c>
-      <c r="P567" s="54"/>
-      <c r="Q567" s="56">
-        <f>+P567</f>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" s="1">
+      <c r="F572" s="10">
+        <f>E572*0.666*24/72</f>
+      </c>
+      <c r="G572" s="54">
+        <v>0</v>
+      </c>
+      <c r="H572" s="54">
+        <v>0</v>
+      </c>
+      <c r="I572" s="54">
+        <v>0</v>
+      </c>
+      <c r="J572" s="54">
+        <v>0</v>
+      </c>
+      <c r="K572" s="54">
+        <v>0</v>
+      </c>
+      <c r="L572" s="55">
+        <v>0</v>
+      </c>
+      <c r="M572" s="54">
+        <v>0</v>
+      </c>
+      <c r="N572" s="55">
+        <v>0</v>
+      </c>
+      <c r="O572" s="10">
+        <v>0</v>
+      </c>
+      <c r="P572" s="54"/>
+      <c r="Q572" s="56">
+        <f>+P572</f>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1">
         <v>39103</v>
       </c>
-      <c r="B568" s="52">
+      <c r="B573" s="52">
         <v>10101</v>
       </c>
-      <c r="C568" s="53" t="inlineStr">
+      <c r="C573" s="53" t="inlineStr">
         <is>
           <t>EL CALVARIO</t>
         </is>
       </c>
-      <c r="D568" s="57">
+      <c r="D573" s="57">
         <v>166</v>
       </c>
-      <c r="E568" s="57">
+      <c r="E573" s="57">
         <v>291</v>
       </c>
-      <c r="F568" s="10">
-        <f>E568*0.666*24/72</f>
-      </c>
-      <c r="G568" s="54">
-        <v>0</v>
-      </c>
-      <c r="H568" s="54">
-        <v>0</v>
-      </c>
-      <c r="I568" s="54">
-        <v>0</v>
-      </c>
-      <c r="J568" s="54">
-        <v>0</v>
-      </c>
-      <c r="K568" s="54">
-        <v>0</v>
-      </c>
-      <c r="L568" s="55">
-        <v>0</v>
-      </c>
-      <c r="M568" s="54">
-        <v>0</v>
-      </c>
-      <c r="N568" s="55">
-        <v>0</v>
-      </c>
-      <c r="O568" s="10">
-        <v>0</v>
-      </c>
-      <c r="P568" s="54"/>
-      <c r="Q568" s="56">
-        <f>+P568</f>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" s="1">
+      <c r="F573" s="10">
+        <f>E573*0.666*24/72</f>
+      </c>
+      <c r="G573" s="54">
+        <v>0</v>
+      </c>
+      <c r="H573" s="54">
+        <v>0</v>
+      </c>
+      <c r="I573" s="54">
+        <v>0</v>
+      </c>
+      <c r="J573" s="54">
+        <v>0</v>
+      </c>
+      <c r="K573" s="54">
+        <v>0</v>
+      </c>
+      <c r="L573" s="55">
+        <v>0</v>
+      </c>
+      <c r="M573" s="54">
+        <v>0</v>
+      </c>
+      <c r="N573" s="55">
+        <v>0</v>
+      </c>
+      <c r="O573" s="10">
+        <v>0</v>
+      </c>
+      <c r="P573" s="54"/>
+      <c r="Q573" s="56">
+        <f>+P573</f>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1">
         <v>39104</v>
       </c>
-      <c r="B569" s="52">
+      <c r="B574" s="52">
         <v>10101</v>
       </c>
-      <c r="C569" s="53" t="inlineStr">
+      <c r="C574" s="53" t="inlineStr">
         <is>
           <t>STA  ROSA 2A SECCION</t>
         </is>
       </c>
-      <c r="D569" s="57">
+      <c r="D574" s="57">
         <v>137</v>
       </c>
-      <c r="E569" s="57">
+      <c r="E574" s="57">
         <v>215</v>
       </c>
-      <c r="F569" s="10">
-        <f>E569*0.666*24/72</f>
-      </c>
-      <c r="G569" s="54">
-        <v>0</v>
-      </c>
-      <c r="H569" s="54">
-        <v>0</v>
-      </c>
-      <c r="I569" s="54">
-        <v>0</v>
-      </c>
-      <c r="J569" s="54">
-        <v>0</v>
-      </c>
-      <c r="K569" s="54">
-        <v>0</v>
-      </c>
-      <c r="L569" s="55">
-        <v>0</v>
-      </c>
-      <c r="M569" s="54">
-        <v>0</v>
-      </c>
-      <c r="N569" s="55">
-        <v>0</v>
-      </c>
-      <c r="O569" s="10">
-        <v>0</v>
-      </c>
-      <c r="P569" s="54"/>
-      <c r="Q569" s="56">
-        <f>+P569</f>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" s="1">
+      <c r="F574" s="10">
+        <f>E574*0.666*24/72</f>
+      </c>
+      <c r="G574" s="54">
+        <v>0</v>
+      </c>
+      <c r="H574" s="54">
+        <v>0</v>
+      </c>
+      <c r="I574" s="54">
+        <v>0</v>
+      </c>
+      <c r="J574" s="54">
+        <v>0</v>
+      </c>
+      <c r="K574" s="54">
+        <v>0</v>
+      </c>
+      <c r="L574" s="55">
+        <v>0</v>
+      </c>
+      <c r="M574" s="54">
+        <v>0</v>
+      </c>
+      <c r="N574" s="55">
+        <v>0</v>
+      </c>
+      <c r="O574" s="10">
+        <v>0</v>
+      </c>
+      <c r="P574" s="54"/>
+      <c r="Q574" s="56">
+        <f>+P574</f>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1">
         <v>39105</v>
       </c>
-      <c r="B570" s="52">
+      <c r="B575" s="52">
         <v>10101</v>
       </c>
-      <c r="C570" s="53" t="inlineStr">
+      <c r="C575" s="53" t="inlineStr">
         <is>
           <t>LOS ALAMOS</t>
         </is>
       </c>
-      <c r="D570" s="57">
+      <c r="D575" s="57">
         <v>222</v>
       </c>
-      <c r="E570" s="57">
+      <c r="E575" s="57">
         <v>366</v>
       </c>
-      <c r="F570" s="10">
-        <f>E570*0.666*24/72</f>
-      </c>
-      <c r="G570" s="54">
-        <v>0</v>
-      </c>
-      <c r="H570" s="54">
-        <v>0</v>
-      </c>
-      <c r="I570" s="54">
-        <v>0</v>
-      </c>
-      <c r="J570" s="54">
-        <v>0</v>
-      </c>
-      <c r="K570" s="54">
-        <v>0</v>
-      </c>
-      <c r="L570" s="55">
-        <v>0</v>
-      </c>
-      <c r="M570" s="54">
-        <v>0</v>
-      </c>
-      <c r="N570" s="55">
-        <v>0</v>
-      </c>
-      <c r="O570" s="10">
-        <v>0</v>
-      </c>
-      <c r="P570" s="54"/>
-      <c r="Q570" s="56">
-        <f>+P570</f>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" s="1">
+      <c r="F575" s="10">
+        <f>E575*0.666*24/72</f>
+      </c>
+      <c r="G575" s="54">
+        <v>0</v>
+      </c>
+      <c r="H575" s="54">
+        <v>0</v>
+      </c>
+      <c r="I575" s="54">
+        <v>0</v>
+      </c>
+      <c r="J575" s="54">
+        <v>0</v>
+      </c>
+      <c r="K575" s="54">
+        <v>0</v>
+      </c>
+      <c r="L575" s="55">
+        <v>0</v>
+      </c>
+      <c r="M575" s="54">
+        <v>0</v>
+      </c>
+      <c r="N575" s="55">
+        <v>0</v>
+      </c>
+      <c r="O575" s="10">
+        <v>0</v>
+      </c>
+      <c r="P575" s="54"/>
+      <c r="Q575" s="56">
+        <f>+P575</f>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1">
         <v>39106</v>
       </c>
-      <c r="B571" s="52">
+      <c r="B576" s="52">
         <v>10101</v>
       </c>
-      <c r="C571" s="53" t="inlineStr">
+      <c r="C576" s="53" t="inlineStr">
         <is>
           <t>EL MIRADOR</t>
         </is>
       </c>
-      <c r="D571" s="57">
+      <c r="D576" s="57">
         <v>107</v>
       </c>
-      <c r="E571" s="57">
+      <c r="E576" s="57">
         <v>156</v>
       </c>
-      <c r="F571" s="10">
-        <f>E571*0.666*24/72</f>
-      </c>
-      <c r="G571" s="54">
-        <v>0</v>
-      </c>
-      <c r="H571" s="54">
-        <v>0</v>
-      </c>
-      <c r="I571" s="54">
-        <v>0</v>
-      </c>
-      <c r="J571" s="54">
-        <v>0</v>
-      </c>
-      <c r="K571" s="54">
-        <v>0</v>
-      </c>
-      <c r="L571" s="55">
-        <v>0</v>
-      </c>
-      <c r="M571" s="54">
-        <v>0</v>
-      </c>
-      <c r="N571" s="55">
-        <v>0</v>
-      </c>
-      <c r="O571" s="10">
-        <v>0</v>
-      </c>
-      <c r="P571" s="54"/>
-      <c r="Q571" s="56">
-        <f>+P571</f>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" s="1">
+      <c r="F576" s="10">
+        <f>E576*0.666*24/72</f>
+      </c>
+      <c r="G576" s="54">
+        <v>0</v>
+      </c>
+      <c r="H576" s="54">
+        <v>0</v>
+      </c>
+      <c r="I576" s="54">
+        <v>0</v>
+      </c>
+      <c r="J576" s="54">
+        <v>0</v>
+      </c>
+      <c r="K576" s="54">
+        <v>0</v>
+      </c>
+      <c r="L576" s="55">
+        <v>0</v>
+      </c>
+      <c r="M576" s="54">
+        <v>0</v>
+      </c>
+      <c r="N576" s="55">
+        <v>0</v>
+      </c>
+      <c r="O576" s="10">
+        <v>0</v>
+      </c>
+      <c r="P576" s="54"/>
+      <c r="Q576" s="56">
+        <f>+P576</f>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1">
         <v>39108</v>
       </c>
-      <c r="B572" s="52">
+      <c r="B577" s="52">
         <v>10101</v>
       </c>
-      <c r="C572" s="53" t="inlineStr">
+      <c r="C577" s="53" t="inlineStr">
         <is>
           <t>TEPEYAC</t>
         </is>
       </c>
-      <c r="D572" s="57">
+      <c r="D577" s="57">
         <v>126</v>
       </c>
-      <c r="E572" s="57">
+      <c r="E577" s="57">
         <v>213</v>
       </c>
-      <c r="F572" s="10">
-        <f>E572*0.666*24/72</f>
-      </c>
-      <c r="G572" s="54">
-        <v>0</v>
-      </c>
-      <c r="H572" s="54">
-        <v>0</v>
-      </c>
-      <c r="I572" s="54">
-        <v>0</v>
-      </c>
-      <c r="J572" s="54">
-        <v>0</v>
-      </c>
-      <c r="K572" s="54">
-        <v>0</v>
-      </c>
-      <c r="L572" s="55">
-        <v>0</v>
-      </c>
-      <c r="M572" s="54">
-        <v>0</v>
-      </c>
-      <c r="N572" s="55">
-        <v>0</v>
-      </c>
-      <c r="O572" s="10">
-        <v>0</v>
-      </c>
-      <c r="P572" s="54"/>
-      <c r="Q572" s="56">
-        <f>+P572</f>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" s="1">
+      <c r="F577" s="10">
+        <f>E577*0.666*24/72</f>
+      </c>
+      <c r="G577" s="54">
+        <v>0</v>
+      </c>
+      <c r="H577" s="54">
+        <v>0</v>
+      </c>
+      <c r="I577" s="54">
+        <v>0</v>
+      </c>
+      <c r="J577" s="54">
+        <v>0</v>
+      </c>
+      <c r="K577" s="54">
+        <v>0</v>
+      </c>
+      <c r="L577" s="55">
+        <v>0</v>
+      </c>
+      <c r="M577" s="54">
+        <v>0</v>
+      </c>
+      <c r="N577" s="55">
+        <v>0</v>
+      </c>
+      <c r="O577" s="10">
+        <v>0</v>
+      </c>
+      <c r="P577" s="54"/>
+      <c r="Q577" s="56">
+        <f>+P577</f>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1">
         <v>39110</v>
       </c>
-      <c r="B573" s="52">
+      <c r="B578" s="52">
         <v>10101</v>
       </c>
-      <c r="C573" s="53" t="inlineStr">
+      <c r="C578" s="53" t="inlineStr">
         <is>
           <t>REFORMA</t>
         </is>
       </c>
-      <c r="D573" s="57">
+      <c r="D578" s="57">
         <v>102</v>
       </c>
-      <c r="E573" s="57">
+      <c r="E578" s="57">
         <v>171</v>
       </c>
-      <c r="F573" s="10">
-        <f>E573*0.666*24/72</f>
-      </c>
-      <c r="G573" s="54">
-        <v>0</v>
-      </c>
-      <c r="H573" s="54">
-        <v>0</v>
-      </c>
-      <c r="I573" s="54">
-        <v>0</v>
-      </c>
-      <c r="J573" s="54">
-        <v>0</v>
-      </c>
-      <c r="K573" s="54">
-        <v>0</v>
-      </c>
-      <c r="L573" s="55">
-        <v>0</v>
-      </c>
-      <c r="M573" s="54">
-        <v>0</v>
-      </c>
-      <c r="N573" s="55">
-        <v>0</v>
-      </c>
-      <c r="O573" s="10">
-        <v>0</v>
-      </c>
-      <c r="P573" s="54"/>
-      <c r="Q573" s="56">
-        <f>+P573</f>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" s="1">
+      <c r="F578" s="10">
+        <f>E578*0.666*24/72</f>
+      </c>
+      <c r="G578" s="54">
+        <v>0</v>
+      </c>
+      <c r="H578" s="54">
+        <v>0</v>
+      </c>
+      <c r="I578" s="54">
+        <v>0</v>
+      </c>
+      <c r="J578" s="54">
+        <v>0</v>
+      </c>
+      <c r="K578" s="54">
+        <v>0</v>
+      </c>
+      <c r="L578" s="55">
+        <v>0</v>
+      </c>
+      <c r="M578" s="54">
+        <v>0</v>
+      </c>
+      <c r="N578" s="55">
+        <v>0</v>
+      </c>
+      <c r="O578" s="10">
+        <v>0</v>
+      </c>
+      <c r="P578" s="54"/>
+      <c r="Q578" s="56">
+        <f>+P578</f>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1">
         <v>39111</v>
       </c>
-      <c r="B574" s="52">
+      <c r="B579" s="52">
         <v>10101</v>
       </c>
-      <c r="C574" s="53" t="inlineStr">
+      <c r="C579" s="53" t="inlineStr">
         <is>
           <t>COLONIA DEL MAESTRO</t>
         </is>
       </c>
-      <c r="D574" s="57">
+      <c r="D579" s="57">
         <v>134</v>
       </c>
-      <c r="E574" s="57">
+      <c r="E579" s="57">
         <v>216</v>
       </c>
-      <c r="F574" s="10">
-        <f>E574*0.666*24/72</f>
-      </c>
-      <c r="G574" s="54">
-        <v>0</v>
-      </c>
-      <c r="H574" s="54">
-        <v>0</v>
-      </c>
-      <c r="I574" s="54">
-        <v>0</v>
-      </c>
-      <c r="J574" s="54">
-        <v>0</v>
-      </c>
-      <c r="K574" s="54">
-        <v>0</v>
-      </c>
-      <c r="L574" s="55">
-        <v>0</v>
-      </c>
-      <c r="M574" s="54">
-        <v>0</v>
-      </c>
-      <c r="N574" s="55">
-        <v>0</v>
-      </c>
-      <c r="O574" s="10">
-        <v>0</v>
-      </c>
-      <c r="P574" s="54"/>
-      <c r="Q574" s="56">
-        <f>+P574</f>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" s="1">
+      <c r="F579" s="10">
+        <f>E579*0.666*24/72</f>
+      </c>
+      <c r="G579" s="54">
+        <v>0</v>
+      </c>
+      <c r="H579" s="54">
+        <v>0</v>
+      </c>
+      <c r="I579" s="54">
+        <v>0</v>
+      </c>
+      <c r="J579" s="54">
+        <v>0</v>
+      </c>
+      <c r="K579" s="54">
+        <v>0</v>
+      </c>
+      <c r="L579" s="55">
+        <v>0</v>
+      </c>
+      <c r="M579" s="54">
+        <v>0</v>
+      </c>
+      <c r="N579" s="55">
+        <v>0</v>
+      </c>
+      <c r="O579" s="10">
+        <v>0</v>
+      </c>
+      <c r="P579" s="54"/>
+      <c r="Q579" s="56">
+        <f>+P579</f>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1">
         <v>39116</v>
       </c>
-      <c r="B575" s="52">
+      <c r="B580" s="52">
         <v>10101</v>
       </c>
-      <c r="C575" s="53" t="inlineStr">
+      <c r="C580" s="53" t="inlineStr">
         <is>
           <t>AGUA DULCE</t>
         </is>
       </c>
-      <c r="D575" s="57">
+      <c r="D580" s="57">
         <v>75</v>
       </c>
-      <c r="E575" s="57">
+      <c r="E580" s="57">
         <v>107</v>
       </c>
-      <c r="F575" s="10">
-        <f>E575*0.666*24/72</f>
-      </c>
-      <c r="G575" s="54">
-        <v>0</v>
-      </c>
-      <c r="H575" s="54">
-        <v>0</v>
-      </c>
-      <c r="I575" s="54">
-        <v>0</v>
-      </c>
-      <c r="J575" s="54">
-        <v>0</v>
-      </c>
-      <c r="K575" s="54">
-        <v>0</v>
-      </c>
-      <c r="L575" s="55">
-        <v>0</v>
-      </c>
-      <c r="M575" s="54">
-        <v>0</v>
-      </c>
-      <c r="N575" s="55">
-        <v>0</v>
-      </c>
-      <c r="O575" s="10">
-        <v>0</v>
-      </c>
-      <c r="P575" s="54"/>
-      <c r="Q575" s="56">
-        <f>+P575</f>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" s="1">
+      <c r="F580" s="10">
+        <f>E580*0.666*24/72</f>
+      </c>
+      <c r="G580" s="54">
+        <v>0</v>
+      </c>
+      <c r="H580" s="54">
+        <v>0</v>
+      </c>
+      <c r="I580" s="54">
+        <v>0</v>
+      </c>
+      <c r="J580" s="54">
+        <v>0</v>
+      </c>
+      <c r="K580" s="54">
+        <v>0</v>
+      </c>
+      <c r="L580" s="55">
+        <v>0</v>
+      </c>
+      <c r="M580" s="54">
+        <v>0</v>
+      </c>
+      <c r="N580" s="55">
+        <v>0</v>
+      </c>
+      <c r="O580" s="10">
+        <v>0</v>
+      </c>
+      <c r="P580" s="54"/>
+      <c r="Q580" s="56">
+        <f>+P580</f>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1">
         <v>43112</v>
       </c>
-      <c r="B576" s="52">
+      <c r="B581" s="52">
         <v>10101</v>
       </c>
-      <c r="C576" s="53" t="inlineStr">
+      <c r="C581" s="53" t="inlineStr">
         <is>
           <t>JUCHITAN DE ZARAGOZA</t>
         </is>
       </c>
-      <c r="D576" s="57">
+      <c r="D581" s="57">
         <v>121</v>
       </c>
-      <c r="E576" s="57">
+      <c r="E581" s="57">
         <v>145</v>
       </c>
-      <c r="F576" s="10">
-        <f>E576*0.666*24/72</f>
-      </c>
-      <c r="G576" s="54">
-        <v>0</v>
-      </c>
-      <c r="H576" s="54">
-        <v>0</v>
-      </c>
-      <c r="I576" s="54">
-        <v>0</v>
-      </c>
-      <c r="J576" s="54">
-        <v>0</v>
-      </c>
-      <c r="K576" s="54">
-        <v>0</v>
-      </c>
-      <c r="L576" s="55">
-        <v>0</v>
-      </c>
-      <c r="M576" s="54">
-        <v>0</v>
-      </c>
-      <c r="N576" s="55">
-        <v>0</v>
-      </c>
-      <c r="O576" s="10">
-        <v>0</v>
-      </c>
-      <c r="P576" s="54"/>
-      <c r="Q576" s="56">
-        <f>+P576</f>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" s="1">
+      <c r="F581" s="10">
+        <f>E581*0.666*24/72</f>
+      </c>
+      <c r="G581" s="54">
+        <v>0</v>
+      </c>
+      <c r="H581" s="54">
+        <v>0</v>
+      </c>
+      <c r="I581" s="54">
+        <v>0</v>
+      </c>
+      <c r="J581" s="54">
+        <v>0</v>
+      </c>
+      <c r="K581" s="54">
+        <v>0</v>
+      </c>
+      <c r="L581" s="55">
+        <v>0</v>
+      </c>
+      <c r="M581" s="54">
+        <v>0</v>
+      </c>
+      <c r="N581" s="55">
+        <v>0</v>
+      </c>
+      <c r="O581" s="10">
+        <v>0</v>
+      </c>
+      <c r="P581" s="54"/>
+      <c r="Q581" s="56">
+        <f>+P581</f>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1">
         <v>43113</v>
       </c>
-      <c r="B577" s="52">
+      <c r="B582" s="52">
         <v>10101</v>
       </c>
-      <c r="C577" s="53" t="inlineStr">
+      <c r="C582" s="53" t="inlineStr">
         <is>
           <t>PLANTA IMPREGNADORA</t>
         </is>
       </c>
-      <c r="D577" s="57">
+      <c r="D582" s="57">
         <v>98</v>
       </c>
-      <c r="E577" s="57">
+      <c r="E582" s="57">
         <v>170</v>
       </c>
-      <c r="F577" s="10">
-        <f>E577*0.666*24/72</f>
-      </c>
-      <c r="G577" s="54">
-        <v>0</v>
-      </c>
-      <c r="H577" s="54">
-        <v>0</v>
-      </c>
-      <c r="I577" s="54">
-        <v>0</v>
-      </c>
-      <c r="J577" s="54">
-        <v>0</v>
-      </c>
-      <c r="K577" s="54">
-        <v>0</v>
-      </c>
-      <c r="L577" s="55">
-        <v>0</v>
-      </c>
-      <c r="M577" s="54">
-        <v>0</v>
-      </c>
-      <c r="N577" s="55">
-        <v>0</v>
-      </c>
-      <c r="O577" s="10">
-        <v>0</v>
-      </c>
-      <c r="P577" s="54"/>
-      <c r="Q577" s="56">
-        <f>+P577</f>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" s="1">
+      <c r="F582" s="10">
+        <f>E582*0.666*24/72</f>
+      </c>
+      <c r="G582" s="54">
+        <v>0</v>
+      </c>
+      <c r="H582" s="54">
+        <v>0</v>
+      </c>
+      <c r="I582" s="54">
+        <v>0</v>
+      </c>
+      <c r="J582" s="54">
+        <v>0</v>
+      </c>
+      <c r="K582" s="54">
+        <v>0</v>
+      </c>
+      <c r="L582" s="55">
+        <v>0</v>
+      </c>
+      <c r="M582" s="54">
+        <v>0</v>
+      </c>
+      <c r="N582" s="55">
+        <v>0</v>
+      </c>
+      <c r="O582" s="10">
+        <v>0</v>
+      </c>
+      <c r="P582" s="54"/>
+      <c r="Q582" s="56">
+        <f>+P582</f>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1">
         <v>44102</v>
       </c>
-      <c r="B578" s="52">
+      <c r="B583" s="52">
         <v>10101</v>
       </c>
-      <c r="C578" s="53" t="inlineStr">
+      <c r="C583" s="53" t="inlineStr">
         <is>
           <t>LOMA BONITA</t>
         </is>
       </c>
-      <c r="D578" s="57">
+      <c r="D583" s="57">
         <v>645</v>
       </c>
-      <c r="E578" s="57">
+      <c r="E583" s="57">
         <v>1139</v>
       </c>
-      <c r="F578" s="10">
-        <f>E578*0.666*24/72</f>
-      </c>
-      <c r="G578" s="54">
-        <v>0</v>
-      </c>
-      <c r="H578" s="54">
-        <v>0</v>
-      </c>
-      <c r="I578" s="54">
-        <v>0</v>
-      </c>
-      <c r="J578" s="54">
-        <v>0</v>
-      </c>
-      <c r="K578" s="54">
-        <v>0</v>
-      </c>
-      <c r="L578" s="55">
-        <v>0</v>
-      </c>
-      <c r="M578" s="54">
-        <v>0</v>
-      </c>
-      <c r="N578" s="55">
-        <v>0</v>
-      </c>
-      <c r="O578" s="10">
-        <v>0</v>
-      </c>
-      <c r="P578" s="54"/>
-      <c r="Q578" s="56">
-        <f>+P578</f>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" s="1">
+      <c r="F583" s="10">
+        <f>E583*0.666*24/72</f>
+      </c>
+      <c r="G583" s="54">
+        <v>0</v>
+      </c>
+      <c r="H583" s="54">
+        <v>0</v>
+      </c>
+      <c r="I583" s="54">
+        <v>0</v>
+      </c>
+      <c r="J583" s="54">
+        <v>0</v>
+      </c>
+      <c r="K583" s="54">
+        <v>0</v>
+      </c>
+      <c r="L583" s="55">
+        <v>0</v>
+      </c>
+      <c r="M583" s="54">
+        <v>0</v>
+      </c>
+      <c r="N583" s="55">
+        <v>0</v>
+      </c>
+      <c r="O583" s="10">
+        <v>0</v>
+      </c>
+      <c r="P583" s="54"/>
+      <c r="Q583" s="56">
+        <f>+P583</f>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1">
         <v>44104</v>
       </c>
-      <c r="B579" s="52">
+      <c r="B584" s="52">
         <v>10101</v>
       </c>
-      <c r="C579" s="53" t="inlineStr">
+      <c r="C584" s="53" t="inlineStr">
         <is>
           <t>BARRIO EL CONEJO</t>
         </is>
       </c>
-      <c r="D579" s="57">
+      <c r="D584" s="57">
         <v>124</v>
       </c>
-      <c r="E579" s="57">
+      <c r="E584" s="57">
         <v>198</v>
       </c>
-      <c r="F579" s="10">
-        <f>E579*0.666*24/72</f>
-      </c>
-      <c r="G579" s="54">
-        <v>0</v>
-      </c>
-      <c r="H579" s="54">
-        <v>0</v>
-      </c>
-      <c r="I579" s="54">
-        <v>0</v>
-      </c>
-      <c r="J579" s="54">
-        <v>0</v>
-      </c>
-      <c r="K579" s="54">
-        <v>0</v>
-      </c>
-      <c r="L579" s="55">
-        <v>0</v>
-      </c>
-      <c r="M579" s="54">
-        <v>0</v>
-      </c>
-      <c r="N579" s="55">
-        <v>0</v>
-      </c>
-      <c r="O579" s="10">
-        <v>0</v>
-      </c>
-      <c r="P579" s="54"/>
-      <c r="Q579" s="56">
-        <f>+P579</f>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" s="1">
+      <c r="F584" s="10">
+        <f>E584*0.666*24/72</f>
+      </c>
+      <c r="G584" s="54">
+        <v>0</v>
+      </c>
+      <c r="H584" s="54">
+        <v>0</v>
+      </c>
+      <c r="I584" s="54">
+        <v>0</v>
+      </c>
+      <c r="J584" s="54">
+        <v>0</v>
+      </c>
+      <c r="K584" s="54">
+        <v>0</v>
+      </c>
+      <c r="L584" s="55">
+        <v>0</v>
+      </c>
+      <c r="M584" s="54">
+        <v>0</v>
+      </c>
+      <c r="N584" s="55">
+        <v>0</v>
+      </c>
+      <c r="O584" s="10">
+        <v>0</v>
+      </c>
+      <c r="P584" s="54"/>
+      <c r="Q584" s="56">
+        <f>+P584</f>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1">
         <v>44105</v>
       </c>
-      <c r="B580" s="52">
+      <c r="B585" s="52">
         <v>10101</v>
       </c>
-      <c r="C580" s="53" t="inlineStr">
+      <c r="C585" s="53" t="inlineStr">
         <is>
           <t>LAS PI AS</t>
         </is>
       </c>
-      <c r="D580" s="57">
+      <c r="D585" s="57">
         <v>132</v>
       </c>
-      <c r="E580" s="57">
+      <c r="E585" s="57">
         <v>194</v>
       </c>
-      <c r="F580" s="10">
-        <f>E580*0.666*24/72</f>
-      </c>
-      <c r="G580" s="54">
-        <v>0</v>
-      </c>
-      <c r="H580" s="54">
-        <v>0</v>
-      </c>
-      <c r="I580" s="54">
-        <v>0</v>
-      </c>
-      <c r="J580" s="54">
-        <v>0</v>
-      </c>
-      <c r="K580" s="54">
-        <v>0</v>
-      </c>
-      <c r="L580" s="55">
-        <v>0</v>
-      </c>
-      <c r="M580" s="54">
-        <v>0</v>
-      </c>
-      <c r="N580" s="55">
-        <v>0</v>
-      </c>
-      <c r="O580" s="10">
-        <v>0</v>
-      </c>
-      <c r="P580" s="54"/>
-      <c r="Q580" s="56">
-        <f>+P580</f>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" s="1">
+      <c r="F585" s="10">
+        <f>E585*0.666*24/72</f>
+      </c>
+      <c r="G585" s="54">
+        <v>0</v>
+      </c>
+      <c r="H585" s="54">
+        <v>0</v>
+      </c>
+      <c r="I585" s="54">
+        <v>0</v>
+      </c>
+      <c r="J585" s="54">
+        <v>0</v>
+      </c>
+      <c r="K585" s="54">
+        <v>0</v>
+      </c>
+      <c r="L585" s="55">
+        <v>0</v>
+      </c>
+      <c r="M585" s="54">
+        <v>0</v>
+      </c>
+      <c r="N585" s="55">
+        <v>0</v>
+      </c>
+      <c r="O585" s="10">
+        <v>0</v>
+      </c>
+      <c r="P585" s="54"/>
+      <c r="Q585" s="56">
+        <f>+P585</f>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1">
         <v>44109</v>
       </c>
-      <c r="B581" s="52">
+      <c r="B586" s="52">
         <v>10101</v>
       </c>
-      <c r="C581" s="53" t="inlineStr">
+      <c r="C586" s="53" t="inlineStr">
         <is>
           <t>SAN ANTONIO</t>
         </is>
       </c>
-      <c r="D581" s="57">
+      <c r="D586" s="57">
         <v>89</v>
       </c>
-      <c r="E581" s="57">
+      <c r="E586" s="57">
         <v>134</v>
       </c>
-      <c r="F581" s="10">
-        <f>E581*0.666*24/72</f>
-      </c>
-      <c r="G581" s="54">
-        <v>0</v>
-      </c>
-      <c r="H581" s="54">
-        <v>0</v>
-      </c>
-      <c r="I581" s="54">
-        <v>0</v>
-      </c>
-      <c r="J581" s="54">
-        <v>0</v>
-      </c>
-      <c r="K581" s="54">
-        <v>0</v>
-      </c>
-      <c r="L581" s="55">
-        <v>0</v>
-      </c>
-      <c r="M581" s="54">
-        <v>0</v>
-      </c>
-      <c r="N581" s="55">
-        <v>0</v>
-      </c>
-      <c r="O581" s="10">
-        <v>0</v>
-      </c>
-      <c r="P581" s="54"/>
-      <c r="Q581" s="56">
-        <f>+P581</f>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" s="1">
+      <c r="F586" s="10">
+        <f>E586*0.666*24/72</f>
+      </c>
+      <c r="G586" s="54">
+        <v>0</v>
+      </c>
+      <c r="H586" s="54">
+        <v>0</v>
+      </c>
+      <c r="I586" s="54">
+        <v>0</v>
+      </c>
+      <c r="J586" s="54">
+        <v>0</v>
+      </c>
+      <c r="K586" s="54">
+        <v>0</v>
+      </c>
+      <c r="L586" s="55">
+        <v>0</v>
+      </c>
+      <c r="M586" s="54">
+        <v>0</v>
+      </c>
+      <c r="N586" s="55">
+        <v>0</v>
+      </c>
+      <c r="O586" s="10">
+        <v>0</v>
+      </c>
+      <c r="P586" s="54"/>
+      <c r="Q586" s="56">
+        <f>+P586</f>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1">
         <v>44110</v>
       </c>
-      <c r="B582" s="52">
+      <c r="B587" s="52">
         <v>10101</v>
       </c>
-      <c r="C582" s="53" t="inlineStr">
+      <c r="C587" s="53" t="inlineStr">
         <is>
           <t>ODILON MINA</t>
         </is>
       </c>
-      <c r="D582" s="57">
+      <c r="D587" s="57">
         <v>99</v>
       </c>
-      <c r="E582" s="57">
+      <c r="E587" s="57">
         <v>158</v>
       </c>
-      <c r="F582" s="10">
-        <f>E582*0.666*24/72</f>
-      </c>
-      <c r="G582" s="54">
-        <v>0</v>
-      </c>
-      <c r="H582" s="54">
-        <v>0</v>
-      </c>
-      <c r="I582" s="54">
-        <v>0</v>
-      </c>
-      <c r="J582" s="54">
-        <v>0</v>
-      </c>
-      <c r="K582" s="54">
-        <v>0</v>
-      </c>
-      <c r="L582" s="55">
-        <v>0</v>
-      </c>
-      <c r="M582" s="54">
-        <v>0</v>
-      </c>
-      <c r="N582" s="55">
-        <v>0</v>
-      </c>
-      <c r="O582" s="10">
-        <v>0</v>
-      </c>
-      <c r="P582" s="54"/>
-      <c r="Q582" s="56">
-        <f>+P582</f>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" s="1">
+      <c r="F587" s="10">
+        <f>E587*0.666*24/72</f>
+      </c>
+      <c r="G587" s="54">
+        <v>0</v>
+      </c>
+      <c r="H587" s="54">
+        <v>0</v>
+      </c>
+      <c r="I587" s="54">
+        <v>0</v>
+      </c>
+      <c r="J587" s="54">
+        <v>0</v>
+      </c>
+      <c r="K587" s="54">
+        <v>0</v>
+      </c>
+      <c r="L587" s="55">
+        <v>0</v>
+      </c>
+      <c r="M587" s="54">
+        <v>0</v>
+      </c>
+      <c r="N587" s="55">
+        <v>0</v>
+      </c>
+      <c r="O587" s="10">
+        <v>0</v>
+      </c>
+      <c r="P587" s="54"/>
+      <c r="Q587" s="56">
+        <f>+P587</f>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1">
         <v>54101</v>
       </c>
-      <c r="B583" s="52">
+      <c r="B588" s="52">
         <v>10101</v>
       </c>
-      <c r="C583" s="53" t="inlineStr">
+      <c r="C588" s="53" t="inlineStr">
         <is>
           <t>MAGDALENA ZAHUATLAN</t>
         </is>
       </c>
-      <c r="D583" s="57">
+      <c r="D588" s="57">
         <v>45</v>
       </c>
-      <c r="E583" s="57">
+      <c r="E588" s="57">
         <v>59</v>
       </c>
-      <c r="F583" s="10">
-        <f>E583*0.666*24/72</f>
-      </c>
-      <c r="G583" s="54">
-        <v>0</v>
-      </c>
-      <c r="H583" s="54">
-        <v>0</v>
-      </c>
-      <c r="I583" s="54">
-        <v>0</v>
-      </c>
-      <c r="J583" s="54">
-        <v>0</v>
-      </c>
-      <c r="K583" s="54">
-        <v>0</v>
-      </c>
-      <c r="L583" s="55">
-        <v>0</v>
-      </c>
-      <c r="M583" s="54">
-        <v>0</v>
-      </c>
-      <c r="N583" s="55">
-        <v>0</v>
-      </c>
-      <c r="O583" s="10">
-        <v>0</v>
-      </c>
-      <c r="P583" s="54"/>
-      <c r="Q583" s="56">
-        <f>+P583</f>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" s="1">
+      <c r="F588" s="10">
+        <f>E588*0.666*24/72</f>
+      </c>
+      <c r="G588" s="54">
+        <v>0</v>
+      </c>
+      <c r="H588" s="54">
+        <v>0</v>
+      </c>
+      <c r="I588" s="54">
+        <v>0</v>
+      </c>
+      <c r="J588" s="54">
+        <v>0</v>
+      </c>
+      <c r="K588" s="54">
+        <v>0</v>
+      </c>
+      <c r="L588" s="55">
+        <v>0</v>
+      </c>
+      <c r="M588" s="54">
+        <v>0</v>
+      </c>
+      <c r="N588" s="55">
+        <v>0</v>
+      </c>
+      <c r="O588" s="10">
+        <v>0</v>
+      </c>
+      <c r="P588" s="54"/>
+      <c r="Q588" s="56">
+        <f>+P588</f>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1">
         <v>57104</v>
       </c>
-      <c r="B584" s="52">
+      <c r="B589" s="52">
         <v>10101</v>
       </c>
-      <c r="C584" s="53" t="inlineStr">
+      <c r="C589" s="53" t="inlineStr">
         <is>
           <t>BARRIO JUAREZ SUR  (MATIAS )</t>
         </is>
       </c>
-      <c r="D584" s="57">
+      <c r="D589" s="57">
         <v>101</v>
       </c>
-      <c r="E584" s="57">
+      <c r="E589" s="57">
         <v>168</v>
       </c>
-      <c r="F584" s="10">
-        <f>E584*0.666*24/72</f>
-      </c>
-      <c r="G584" s="54">
-        <v>0</v>
-      </c>
-      <c r="H584" s="54">
-        <v>0</v>
-      </c>
-      <c r="I584" s="54">
-        <v>0</v>
-      </c>
-      <c r="J584" s="54">
-        <v>0</v>
-      </c>
-      <c r="K584" s="54">
-        <v>0</v>
-      </c>
-      <c r="L584" s="55">
-        <v>0</v>
-      </c>
-      <c r="M584" s="54">
-        <v>0</v>
-      </c>
-      <c r="N584" s="55">
-        <v>0</v>
-      </c>
-      <c r="O584" s="10">
-        <v>0</v>
-      </c>
-      <c r="P584" s="54"/>
-      <c r="Q584" s="56">
-        <f>+P584</f>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" s="1">
+      <c r="F589" s="10">
+        <f>E589*0.666*24/72</f>
+      </c>
+      <c r="G589" s="54">
+        <v>0</v>
+      </c>
+      <c r="H589" s="54">
+        <v>0</v>
+      </c>
+      <c r="I589" s="54">
+        <v>0</v>
+      </c>
+      <c r="J589" s="54">
+        <v>0</v>
+      </c>
+      <c r="K589" s="54">
+        <v>0</v>
+      </c>
+      <c r="L589" s="55">
+        <v>0</v>
+      </c>
+      <c r="M589" s="54">
+        <v>0</v>
+      </c>
+      <c r="N589" s="55">
+        <v>0</v>
+      </c>
+      <c r="O589" s="10">
+        <v>0</v>
+      </c>
+      <c r="P589" s="54"/>
+      <c r="Q589" s="56">
+        <f>+P589</f>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1">
         <v>57105</v>
       </c>
-      <c r="B585" s="52">
+      <c r="B590" s="52">
         <v>10101</v>
       </c>
-      <c r="C585" s="53" t="inlineStr">
+      <c r="C590" s="53" t="inlineStr">
         <is>
           <t>COL  OAXAQUE A (MATIAS)</t>
         </is>
       </c>
-      <c r="D585" s="57">
+      <c r="D590" s="57">
         <v>185</v>
       </c>
-      <c r="E585" s="57">
+      <c r="E590" s="57">
         <v>288</v>
       </c>
-      <c r="F585" s="10">
-        <f>E585*0.666*24/72</f>
-      </c>
-      <c r="G585" s="54">
-        <v>0</v>
-      </c>
-      <c r="H585" s="54">
-        <v>0</v>
-      </c>
-      <c r="I585" s="54">
-        <v>0</v>
-      </c>
-      <c r="J585" s="54">
-        <v>0</v>
-      </c>
-      <c r="K585" s="54">
-        <v>0</v>
-      </c>
-      <c r="L585" s="55">
-        <v>0</v>
-      </c>
-      <c r="M585" s="54">
-        <v>0</v>
-      </c>
-      <c r="N585" s="55">
-        <v>0</v>
-      </c>
-      <c r="O585" s="10">
-        <v>0</v>
-      </c>
-      <c r="P585" s="54"/>
-      <c r="Q585" s="56">
-        <f>+P585</f>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" s="1">
+      <c r="F590" s="10">
+        <f>E590*0.666*24/72</f>
+      </c>
+      <c r="G590" s="54">
+        <v>0</v>
+      </c>
+      <c r="H590" s="54">
+        <v>0</v>
+      </c>
+      <c r="I590" s="54">
+        <v>0</v>
+      </c>
+      <c r="J590" s="54">
+        <v>0</v>
+      </c>
+      <c r="K590" s="54">
+        <v>0</v>
+      </c>
+      <c r="L590" s="55">
+        <v>0</v>
+      </c>
+      <c r="M590" s="54">
+        <v>0</v>
+      </c>
+      <c r="N590" s="55">
+        <v>0</v>
+      </c>
+      <c r="O590" s="10">
+        <v>0</v>
+      </c>
+      <c r="P590" s="54"/>
+      <c r="Q590" s="56">
+        <f>+P590</f>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1">
         <v>59107</v>
       </c>
-      <c r="B586" s="52">
+      <c r="B591" s="52">
         <v>10101</v>
       </c>
-      <c r="C586" s="53" t="inlineStr">
+      <c r="C591" s="53" t="inlineStr">
         <is>
           <t>MIAHUATLAN DE PORFIRIO DIAZ</t>
         </is>
       </c>
-      <c r="D586" s="57">
+      <c r="D591" s="57">
         <v>165</v>
       </c>
-      <c r="E586" s="57">
+      <c r="E591" s="57">
         <v>263</v>
       </c>
-      <c r="F586" s="10">
-        <f>E586*0.666*24/72</f>
-      </c>
-      <c r="G586" s="54">
-        <v>0</v>
-      </c>
-      <c r="H586" s="54">
-        <v>0</v>
-      </c>
-      <c r="I586" s="54">
-        <v>0</v>
-      </c>
-      <c r="J586" s="54">
-        <v>0</v>
-      </c>
-      <c r="K586" s="54">
-        <v>0</v>
-      </c>
-      <c r="L586" s="55">
-        <v>0</v>
-      </c>
-      <c r="M586" s="54">
-        <v>0</v>
-      </c>
-      <c r="N586" s="55">
-        <v>0</v>
-      </c>
-      <c r="O586" s="10">
-        <v>0</v>
-      </c>
-      <c r="P586" s="54"/>
-      <c r="Q586" s="56">
-        <f>+P586</f>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" s="1">
+      <c r="F591" s="10">
+        <f>E591*0.666*24/72</f>
+      </c>
+      <c r="G591" s="54">
+        <v>0</v>
+      </c>
+      <c r="H591" s="54">
+        <v>0</v>
+      </c>
+      <c r="I591" s="54">
+        <v>0</v>
+      </c>
+      <c r="J591" s="54">
+        <v>0</v>
+      </c>
+      <c r="K591" s="54">
+        <v>0</v>
+      </c>
+      <c r="L591" s="55">
+        <v>0</v>
+      </c>
+      <c r="M591" s="54">
+        <v>0</v>
+      </c>
+      <c r="N591" s="55">
+        <v>0</v>
+      </c>
+      <c r="O591" s="10">
+        <v>0</v>
+      </c>
+      <c r="P591" s="54"/>
+      <c r="Q591" s="56">
+        <f>+P591</f>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1">
         <v>59110</v>
       </c>
-      <c r="B587" s="52">
+      <c r="B592" s="52">
         <v>10101</v>
       </c>
-      <c r="C587" s="53" t="inlineStr">
+      <c r="C592" s="53" t="inlineStr">
         <is>
           <t>MIAHUATLAN CENTRO</t>
         </is>
       </c>
-      <c r="D587" s="57">
+      <c r="D592" s="57">
         <v>283</v>
       </c>
-      <c r="E587" s="57">
+      <c r="E592" s="57">
         <v>429</v>
       </c>
-      <c r="F587" s="10">
-        <f>E587*0.666*24/72</f>
-      </c>
-      <c r="G587" s="54">
-        <v>0</v>
-      </c>
-      <c r="H587" s="54">
-        <v>0</v>
-      </c>
-      <c r="I587" s="54">
-        <v>0</v>
-      </c>
-      <c r="J587" s="54">
-        <v>0</v>
-      </c>
-      <c r="K587" s="54">
-        <v>0</v>
-      </c>
-      <c r="L587" s="55">
-        <v>0</v>
-      </c>
-      <c r="M587" s="54">
-        <v>0</v>
-      </c>
-      <c r="N587" s="55">
-        <v>0</v>
-      </c>
-      <c r="O587" s="10">
-        <v>0</v>
-      </c>
-      <c r="P587" s="54"/>
-      <c r="Q587" s="56">
-        <f>+P587</f>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" s="1">
+      <c r="F592" s="10">
+        <f>E592*0.666*24/72</f>
+      </c>
+      <c r="G592" s="54">
+        <v>0</v>
+      </c>
+      <c r="H592" s="54">
+        <v>0</v>
+      </c>
+      <c r="I592" s="54">
+        <v>0</v>
+      </c>
+      <c r="J592" s="54">
+        <v>0</v>
+      </c>
+      <c r="K592" s="54">
+        <v>0</v>
+      </c>
+      <c r="L592" s="55">
+        <v>0</v>
+      </c>
+      <c r="M592" s="54">
+        <v>0</v>
+      </c>
+      <c r="N592" s="55">
+        <v>0</v>
+      </c>
+      <c r="O592" s="10">
+        <v>0</v>
+      </c>
+      <c r="P592" s="54"/>
+      <c r="Q592" s="56">
+        <f>+P592</f>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1">
         <v>61103</v>
       </c>
-      <c r="B588" s="52">
+      <c r="B593" s="52">
         <v>10101</v>
       </c>
-      <c r="C588" s="53" t="inlineStr">
+      <c r="C593" s="53" t="inlineStr">
         <is>
           <t>MONJAS</t>
         </is>
       </c>
-      <c r="D588" s="57">
+      <c r="D593" s="57">
         <v>263</v>
       </c>
-      <c r="E588" s="57">
+      <c r="E593" s="57">
         <v>511</v>
       </c>
-      <c r="F588" s="10">
-        <f>E588*0.666*24/72</f>
-      </c>
-      <c r="G588" s="54">
-        <v>0</v>
-      </c>
-      <c r="H588" s="54">
-        <v>0</v>
-      </c>
-      <c r="I588" s="54">
-        <v>0</v>
-      </c>
-      <c r="J588" s="54">
-        <v>0</v>
-      </c>
-      <c r="K588" s="54">
-        <v>0</v>
-      </c>
-      <c r="L588" s="55">
-        <v>0</v>
-      </c>
-      <c r="M588" s="54">
-        <v>0</v>
-      </c>
-      <c r="N588" s="55">
-        <v>0</v>
-      </c>
-      <c r="O588" s="10">
-        <v>0</v>
-      </c>
-      <c r="P588" s="54"/>
-      <c r="Q588" s="56">
-        <f>+P588</f>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" s="1">
+      <c r="F593" s="10">
+        <f>E593*0.666*24/72</f>
+      </c>
+      <c r="G593" s="54">
+        <v>0</v>
+      </c>
+      <c r="H593" s="54">
+        <v>0</v>
+      </c>
+      <c r="I593" s="54">
+        <v>0</v>
+      </c>
+      <c r="J593" s="54">
+        <v>0</v>
+      </c>
+      <c r="K593" s="54">
+        <v>0</v>
+      </c>
+      <c r="L593" s="55">
+        <v>0</v>
+      </c>
+      <c r="M593" s="54">
+        <v>0</v>
+      </c>
+      <c r="N593" s="55">
+        <v>0</v>
+      </c>
+      <c r="O593" s="10">
+        <v>0</v>
+      </c>
+      <c r="P593" s="54"/>
+      <c r="Q593" s="56">
+        <f>+P593</f>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1">
         <v>67142</v>
       </c>
-      <c r="B589" s="52">
+      <c r="B594" s="52">
         <v>10101</v>
       </c>
-      <c r="C589" s="53" t="inlineStr">
+      <c r="C594" s="53" t="inlineStr">
         <is>
           <t>FALDAS DEL FORTIN</t>
         </is>
       </c>
-      <c r="D589" s="57">
+      <c r="D594" s="57">
         <v>116</v>
       </c>
-      <c r="E589" s="57">
+      <c r="E594" s="57">
         <v>212</v>
       </c>
-      <c r="F589" s="10">
-        <f>E589*0.666*24/72</f>
-      </c>
-      <c r="G589" s="54">
-        <v>0</v>
-      </c>
-      <c r="H589" s="54">
-        <v>0</v>
-      </c>
-      <c r="I589" s="54">
-        <v>0</v>
-      </c>
-      <c r="J589" s="54">
-        <v>0</v>
-      </c>
-      <c r="K589" s="54">
-        <v>0</v>
-      </c>
-      <c r="L589" s="55">
-        <v>0</v>
-      </c>
-      <c r="M589" s="54">
-        <v>0</v>
-      </c>
-      <c r="N589" s="55">
-        <v>0</v>
-      </c>
-      <c r="O589" s="10">
-        <v>0</v>
-      </c>
-      <c r="P589" s="54"/>
-      <c r="Q589" s="56">
-        <f>+P589</f>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" s="1">
+      <c r="F594" s="10">
+        <f>E594*0.666*24/72</f>
+      </c>
+      <c r="G594" s="54">
+        <v>0</v>
+      </c>
+      <c r="H594" s="54">
+        <v>0</v>
+      </c>
+      <c r="I594" s="54">
+        <v>0</v>
+      </c>
+      <c r="J594" s="54">
+        <v>0</v>
+      </c>
+      <c r="K594" s="54">
+        <v>0</v>
+      </c>
+      <c r="L594" s="55">
+        <v>0</v>
+      </c>
+      <c r="M594" s="54">
+        <v>0</v>
+      </c>
+      <c r="N594" s="55">
+        <v>0</v>
+      </c>
+      <c r="O594" s="10">
+        <v>0</v>
+      </c>
+      <c r="P594" s="54"/>
+      <c r="Q594" s="56">
+        <f>+P594</f>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1">
         <v>79103</v>
       </c>
-      <c r="B590" s="52">
+      <c r="B595" s="52">
         <v>10101</v>
       </c>
-      <c r="C590" s="53" t="inlineStr">
+      <c r="C595" s="53" t="inlineStr">
         <is>
           <t>COLONIA  HIDALGO PONIENTE</t>
         </is>
       </c>
-      <c r="D590" s="57">
+      <c r="D595" s="57">
         <v>607</v>
       </c>
-      <c r="E590" s="57">
+      <c r="E595" s="57">
         <v>978</v>
       </c>
-      <c r="F590" s="10">
-        <f>E590*0.666*24/72</f>
-      </c>
-      <c r="G590" s="54">
-        <v>0</v>
-      </c>
-      <c r="H590" s="54">
-        <v>0</v>
-      </c>
-      <c r="I590" s="54">
-        <v>0</v>
-      </c>
-      <c r="J590" s="54">
-        <v>0</v>
-      </c>
-      <c r="K590" s="54">
-        <v>0</v>
-      </c>
-      <c r="L590" s="55">
-        <v>0</v>
-      </c>
-      <c r="M590" s="54">
-        <v>0</v>
-      </c>
-      <c r="N590" s="55">
-        <v>0</v>
-      </c>
-      <c r="O590" s="10">
-        <v>0</v>
-      </c>
-      <c r="P590" s="54"/>
-      <c r="Q590" s="56">
-        <f>+P590</f>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" s="1">
+      <c r="F595" s="10">
+        <f>E595*0.666*24/72</f>
+      </c>
+      <c r="G595" s="54">
+        <v>0</v>
+      </c>
+      <c r="H595" s="54">
+        <v>0</v>
+      </c>
+      <c r="I595" s="54">
+        <v>0</v>
+      </c>
+      <c r="J595" s="54">
+        <v>0</v>
+      </c>
+      <c r="K595" s="54">
+        <v>0</v>
+      </c>
+      <c r="L595" s="55">
+        <v>0</v>
+      </c>
+      <c r="M595" s="54">
+        <v>0</v>
+      </c>
+      <c r="N595" s="55">
+        <v>0</v>
+      </c>
+      <c r="O595" s="10">
+        <v>0</v>
+      </c>
+      <c r="P595" s="54"/>
+      <c r="Q595" s="56">
+        <f>+P595</f>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1">
         <v>79107</v>
       </c>
-      <c r="B591" s="52">
+      <c r="B596" s="52">
         <v>10101</v>
       </c>
-      <c r="C591" s="53" t="inlineStr">
+      <c r="C596" s="53" t="inlineStr">
         <is>
           <t>SALINA CRUZ ESPINAL</t>
         </is>
       </c>
-      <c r="D591" s="57">
+      <c r="D596" s="57">
         <v>180</v>
       </c>
-      <c r="E591" s="57">
+      <c r="E596" s="57">
         <v>278</v>
       </c>
-      <c r="F591" s="10">
-        <f>E591*0.666*24/72</f>
-      </c>
-      <c r="G591" s="54">
-        <v>0</v>
-      </c>
-      <c r="H591" s="54">
-        <v>0</v>
-      </c>
-      <c r="I591" s="54">
-        <v>0</v>
-      </c>
-      <c r="J591" s="54">
-        <v>0</v>
-      </c>
-      <c r="K591" s="54">
-        <v>0</v>
-      </c>
-      <c r="L591" s="55">
-        <v>0</v>
-      </c>
-      <c r="M591" s="54">
-        <v>0</v>
-      </c>
-      <c r="N591" s="55">
-        <v>0</v>
-      </c>
-      <c r="O591" s="10">
-        <v>0</v>
-      </c>
-      <c r="P591" s="54"/>
-      <c r="Q591" s="56">
-        <f>+P591</f>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" s="1">
+      <c r="F596" s="10">
+        <f>E596*0.666*24/72</f>
+      </c>
+      <c r="G596" s="54">
+        <v>0</v>
+      </c>
+      <c r="H596" s="54">
+        <v>0</v>
+      </c>
+      <c r="I596" s="54">
+        <v>0</v>
+      </c>
+      <c r="J596" s="54">
+        <v>0</v>
+      </c>
+      <c r="K596" s="54">
+        <v>0</v>
+      </c>
+      <c r="L596" s="55">
+        <v>0</v>
+      </c>
+      <c r="M596" s="54">
+        <v>0</v>
+      </c>
+      <c r="N596" s="55">
+        <v>0</v>
+      </c>
+      <c r="O596" s="10">
+        <v>0</v>
+      </c>
+      <c r="P596" s="54"/>
+      <c r="Q596" s="56">
+        <f>+P596</f>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1">
         <v>96101</v>
       </c>
-      <c r="B592" s="52">
+      <c r="B597" s="52">
         <v>10101</v>
       </c>
-      <c r="C592" s="53" t="inlineStr">
+      <c r="C597" s="53" t="inlineStr">
         <is>
           <t>SAN ANDRES SINAXTLA</t>
         </is>
       </c>
-      <c r="D592" s="57">
+      <c r="D597" s="57">
         <v>122</v>
       </c>
-      <c r="E592" s="57">
+      <c r="E597" s="57">
         <v>252</v>
       </c>
-      <c r="F592" s="10">
-        <f>E592*0.666*24/72</f>
-      </c>
-      <c r="G592" s="54">
-        <v>0</v>
-      </c>
-      <c r="H592" s="54">
-        <v>0</v>
-      </c>
-      <c r="I592" s="54">
-        <v>0</v>
-      </c>
-      <c r="J592" s="54">
-        <v>0</v>
-      </c>
-      <c r="K592" s="54">
-        <v>0</v>
-      </c>
-      <c r="L592" s="55">
-        <v>0</v>
-      </c>
-      <c r="M592" s="54">
-        <v>0</v>
-      </c>
-      <c r="N592" s="55">
-        <v>0</v>
-      </c>
-      <c r="O592" s="10">
-        <v>0</v>
-      </c>
-      <c r="P592" s="54"/>
-      <c r="Q592" s="56">
-        <f>+P592</f>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" s="1">
+      <c r="F597" s="10">
+        <f>E597*0.666*24/72</f>
+      </c>
+      <c r="G597" s="54">
+        <v>0</v>
+      </c>
+      <c r="H597" s="54">
+        <v>0</v>
+      </c>
+      <c r="I597" s="54">
+        <v>0</v>
+      </c>
+      <c r="J597" s="54">
+        <v>0</v>
+      </c>
+      <c r="K597" s="54">
+        <v>0</v>
+      </c>
+      <c r="L597" s="55">
+        <v>0</v>
+      </c>
+      <c r="M597" s="54">
+        <v>0</v>
+      </c>
+      <c r="N597" s="55">
+        <v>0</v>
+      </c>
+      <c r="O597" s="10">
+        <v>0</v>
+      </c>
+      <c r="P597" s="54"/>
+      <c r="Q597" s="56">
+        <f>+P597</f>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1">
         <v>100013</v>
       </c>
-      <c r="B593" s="52">
+      <c r="B598" s="52">
         <v>10101</v>
       </c>
-      <c r="C593" s="53" t="inlineStr">
+      <c r="C598" s="53" t="inlineStr">
         <is>
           <t>OCOTLAN DE MORELOS</t>
         </is>
       </c>
-      <c r="D593" s="57">
+      <c r="D598" s="57">
         <v>394</v>
       </c>
-      <c r="E593" s="57">
+      <c r="E598" s="57">
         <v>665</v>
       </c>
-      <c r="F593" s="10">
-        <f>E593*0.666*24/72</f>
-      </c>
-      <c r="G593" s="54">
-        <v>0</v>
-      </c>
-      <c r="H593" s="54">
-        <v>0</v>
-      </c>
-      <c r="I593" s="54">
-        <v>0</v>
-      </c>
-      <c r="J593" s="54">
-        <v>0</v>
-      </c>
-      <c r="K593" s="54">
-        <v>0</v>
-      </c>
-      <c r="L593" s="55">
-        <v>0</v>
-      </c>
-      <c r="M593" s="54">
-        <v>0</v>
-      </c>
-      <c r="N593" s="55">
-        <v>0</v>
-      </c>
-      <c r="O593" s="10">
-        <v>0</v>
-      </c>
-      <c r="P593" s="54"/>
-      <c r="Q593" s="56">
-        <f>+P593</f>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" s="1">
+      <c r="F598" s="10">
+        <f>E598*0.666*24/72</f>
+      </c>
+      <c r="G598" s="54">
+        <v>0</v>
+      </c>
+      <c r="H598" s="54">
+        <v>0</v>
+      </c>
+      <c r="I598" s="54">
+        <v>0</v>
+      </c>
+      <c r="J598" s="54">
+        <v>0</v>
+      </c>
+      <c r="K598" s="54">
+        <v>0</v>
+      </c>
+      <c r="L598" s="55">
+        <v>0</v>
+      </c>
+      <c r="M598" s="54">
+        <v>0</v>
+      </c>
+      <c r="N598" s="55">
+        <v>0</v>
+      </c>
+      <c r="O598" s="10">
+        <v>0</v>
+      </c>
+      <c r="P598" s="54"/>
+      <c r="Q598" s="56">
+        <f>+P598</f>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1">
         <v>110049</v>
       </c>
-      <c r="B594" s="52">
+      <c r="B599" s="52">
         <v>10101</v>
       </c>
-      <c r="C594" s="53" t="inlineStr">
+      <c r="C599" s="53" t="inlineStr">
         <is>
           <t>EJUTLA DE CRESPO</t>
         </is>
       </c>
-      <c r="D594" s="57">
+      <c r="D599" s="57">
         <v>224</v>
       </c>
-      <c r="E594" s="57">
+      <c r="E599" s="57">
         <v>355</v>
       </c>
-      <c r="F594" s="10">
-        <f>E594*0.666*24/72</f>
-      </c>
-      <c r="G594" s="54">
-        <v>0</v>
-      </c>
-      <c r="H594" s="54">
-        <v>0</v>
-      </c>
-      <c r="I594" s="54">
-        <v>0</v>
-      </c>
-      <c r="J594" s="54">
-        <v>0</v>
-      </c>
-      <c r="K594" s="54">
-        <v>0</v>
-      </c>
-      <c r="L594" s="55">
-        <v>0</v>
-      </c>
-      <c r="M594" s="54">
-        <v>0</v>
-      </c>
-      <c r="N594" s="55">
-        <v>0</v>
-      </c>
-      <c r="O594" s="10">
-        <v>0</v>
-      </c>
-      <c r="P594" s="54"/>
-      <c r="Q594" s="56">
-        <f>+P594</f>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" s="1">
+      <c r="F599" s="10">
+        <f>E599*0.666*24/72</f>
+      </c>
+      <c r="G599" s="54">
+        <v>0</v>
+      </c>
+      <c r="H599" s="54">
+        <v>0</v>
+      </c>
+      <c r="I599" s="54">
+        <v>0</v>
+      </c>
+      <c r="J599" s="54">
+        <v>0</v>
+      </c>
+      <c r="K599" s="54">
+        <v>0</v>
+      </c>
+      <c r="L599" s="55">
+        <v>0</v>
+      </c>
+      <c r="M599" s="54">
+        <v>0</v>
+      </c>
+      <c r="N599" s="55">
+        <v>0</v>
+      </c>
+      <c r="O599" s="10">
+        <v>0</v>
+      </c>
+      <c r="P599" s="54"/>
+      <c r="Q599" s="56">
+        <f>+P599</f>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1">
         <v>110106</v>
       </c>
-      <c r="B595" s="52">
+      <c r="B600" s="52">
         <v>10101</v>
       </c>
-      <c r="C595" s="53" t="inlineStr">
+      <c r="C600" s="53" t="inlineStr">
         <is>
           <t>SANTO DOMINGO TEHUANTEPEC</t>
         </is>
       </c>
-      <c r="D595" s="57">
+      <c r="D600" s="57">
         <v>430</v>
       </c>
-      <c r="E595" s="57">
+      <c r="E600" s="57">
         <v>713</v>
       </c>
-      <c r="F595" s="10">
-        <f>E595*0.666*24/72</f>
-      </c>
-      <c r="G595" s="54">
-        <v>0</v>
-      </c>
-      <c r="H595" s="54">
-        <v>0</v>
-      </c>
-      <c r="I595" s="54">
-        <v>0</v>
-      </c>
-      <c r="J595" s="54">
-        <v>0</v>
-      </c>
-      <c r="K595" s="54">
-        <v>0</v>
-      </c>
-      <c r="L595" s="55">
-        <v>0</v>
-      </c>
-      <c r="M595" s="54">
-        <v>0</v>
-      </c>
-      <c r="N595" s="55">
-        <v>0</v>
-      </c>
-      <c r="O595" s="10">
-        <v>0</v>
-      </c>
-      <c r="P595" s="54"/>
-      <c r="Q595" s="56">
-        <f>+P595</f>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" s="1">
+      <c r="F600" s="10">
+        <f>E600*0.666*24/72</f>
+      </c>
+      <c r="G600" s="54">
+        <v>0</v>
+      </c>
+      <c r="H600" s="54">
+        <v>0</v>
+      </c>
+      <c r="I600" s="54">
+        <v>0</v>
+      </c>
+      <c r="J600" s="54">
+        <v>0</v>
+      </c>
+      <c r="K600" s="54">
+        <v>0</v>
+      </c>
+      <c r="L600" s="55">
+        <v>0</v>
+      </c>
+      <c r="M600" s="54">
+        <v>0</v>
+      </c>
+      <c r="N600" s="55">
+        <v>0</v>
+      </c>
+      <c r="O600" s="10">
+        <v>0</v>
+      </c>
+      <c r="P600" s="54"/>
+      <c r="Q600" s="56">
+        <f>+P600</f>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1">
         <v>110109</v>
       </c>
-      <c r="B596" s="52">
+      <c r="B601" s="52">
         <v>10101</v>
       </c>
-      <c r="C596" s="53" t="inlineStr">
+      <c r="C601" s="53" t="inlineStr">
         <is>
           <t>JUCHITAN DE ZARAGOZA</t>
         </is>
       </c>
-      <c r="D596" s="57">
+      <c r="D601" s="57">
         <v>320</v>
       </c>
-      <c r="E596" s="57">
+      <c r="E601" s="57">
         <v>508</v>
       </c>
-      <c r="F596" s="10">
-        <f>E596*0.666*24/72</f>
-      </c>
-      <c r="G596" s="54">
-        <v>0</v>
-      </c>
-      <c r="H596" s="54">
-        <v>0</v>
-      </c>
-      <c r="I596" s="54">
-        <v>0</v>
-      </c>
-      <c r="J596" s="54">
-        <v>0</v>
-      </c>
-      <c r="K596" s="54">
-        <v>0</v>
-      </c>
-      <c r="L596" s="55">
-        <v>0</v>
-      </c>
-      <c r="M596" s="54">
-        <v>0</v>
-      </c>
-      <c r="N596" s="55">
-        <v>0</v>
-      </c>
-      <c r="O596" s="10">
-        <v>0</v>
-      </c>
-      <c r="P596" s="54"/>
-      <c r="Q596" s="56">
-        <f>+P596</f>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" s="1">
+      <c r="F601" s="10">
+        <f>E601*0.666*24/72</f>
+      </c>
+      <c r="G601" s="54">
+        <v>0</v>
+      </c>
+      <c r="H601" s="54">
+        <v>0</v>
+      </c>
+      <c r="I601" s="54">
+        <v>0</v>
+      </c>
+      <c r="J601" s="54">
+        <v>0</v>
+      </c>
+      <c r="K601" s="54">
+        <v>0</v>
+      </c>
+      <c r="L601" s="55">
+        <v>0</v>
+      </c>
+      <c r="M601" s="54">
+        <v>0</v>
+      </c>
+      <c r="N601" s="55">
+        <v>0</v>
+      </c>
+      <c r="O601" s="10">
+        <v>0</v>
+      </c>
+      <c r="P601" s="54"/>
+      <c r="Q601" s="56">
+        <f>+P601</f>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1">
         <v>110130</v>
       </c>
-      <c r="B597" s="52">
+      <c r="B602" s="52">
         <v>10101</v>
       </c>
-      <c r="C597" s="53" t="inlineStr">
+      <c r="C602" s="53" t="inlineStr">
         <is>
           <t>SALINAS DEL MARQUEZ</t>
         </is>
       </c>
-      <c r="D597" s="57">
+      <c r="D602" s="57">
         <v>320</v>
       </c>
-      <c r="E597" s="57">
+      <c r="E602" s="57">
         <v>482</v>
       </c>
-      <c r="F597" s="10">
-        <f>E597*0.666*24/72</f>
-      </c>
-      <c r="G597" s="54">
-        <v>0</v>
-      </c>
-      <c r="H597" s="54">
-        <v>0</v>
-      </c>
-      <c r="I597" s="54">
-        <v>0</v>
-      </c>
-      <c r="J597" s="54">
-        <v>0</v>
-      </c>
-      <c r="K597" s="54">
-        <v>0</v>
-      </c>
-      <c r="L597" s="55">
-        <v>0</v>
-      </c>
-      <c r="M597" s="54">
-        <v>0</v>
-      </c>
-      <c r="N597" s="55">
-        <v>0</v>
-      </c>
-      <c r="O597" s="10">
-        <v>0</v>
-      </c>
-      <c r="P597" s="54"/>
-      <c r="Q597" s="56">
-        <f>+P597</f>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" s="1">
+      <c r="F602" s="10">
+        <f>E602*0.666*24/72</f>
+      </c>
+      <c r="G602" s="54">
+        <v>0</v>
+      </c>
+      <c r="H602" s="54">
+        <v>0</v>
+      </c>
+      <c r="I602" s="54">
+        <v>0</v>
+      </c>
+      <c r="J602" s="54">
+        <v>0</v>
+      </c>
+      <c r="K602" s="54">
+        <v>0</v>
+      </c>
+      <c r="L602" s="55">
+        <v>0</v>
+      </c>
+      <c r="M602" s="54">
+        <v>0</v>
+      </c>
+      <c r="N602" s="55">
+        <v>0</v>
+      </c>
+      <c r="O602" s="10">
+        <v>0</v>
+      </c>
+      <c r="P602" s="54"/>
+      <c r="Q602" s="56">
+        <f>+P602</f>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1">
         <v>110175</v>
       </c>
-      <c r="B598" s="52">
+      <c r="B603" s="52">
         <v>10101</v>
       </c>
-      <c r="C598" s="53" t="inlineStr">
+      <c r="C603" s="53" t="inlineStr">
         <is>
           <t>MATIAS ROMERO</t>
         </is>
       </c>
-      <c r="D598" s="57">
+      <c r="D603" s="57">
         <v>116</v>
       </c>
-      <c r="E598" s="57">
+      <c r="E603" s="57">
         <v>157</v>
       </c>
-      <c r="F598" s="10">
-        <f>E598*0.666*24/72</f>
-      </c>
-      <c r="G598" s="54">
-        <v>0</v>
-      </c>
-      <c r="H598" s="54">
-        <v>0</v>
-      </c>
-      <c r="I598" s="54">
-        <v>0</v>
-      </c>
-      <c r="J598" s="54">
-        <v>0</v>
-      </c>
-      <c r="K598" s="54">
-        <v>0</v>
-      </c>
-      <c r="L598" s="55">
-        <v>0</v>
-      </c>
-      <c r="M598" s="54">
-        <v>0</v>
-      </c>
-      <c r="N598" s="55">
-        <v>0</v>
-      </c>
-      <c r="O598" s="10">
-        <v>0</v>
-      </c>
-      <c r="P598" s="54"/>
-      <c r="Q598" s="56">
-        <f>+P598</f>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" s="1">
+      <c r="F603" s="10">
+        <f>E603*0.666*24/72</f>
+      </c>
+      <c r="G603" s="54">
+        <v>0</v>
+      </c>
+      <c r="H603" s="54">
+        <v>0</v>
+      </c>
+      <c r="I603" s="54">
+        <v>0</v>
+      </c>
+      <c r="J603" s="54">
+        <v>0</v>
+      </c>
+      <c r="K603" s="54">
+        <v>0</v>
+      </c>
+      <c r="L603" s="55">
+        <v>0</v>
+      </c>
+      <c r="M603" s="54">
+        <v>0</v>
+      </c>
+      <c r="N603" s="55">
+        <v>0</v>
+      </c>
+      <c r="O603" s="10">
+        <v>0</v>
+      </c>
+      <c r="P603" s="54"/>
+      <c r="Q603" s="56">
+        <f>+P603</f>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1">
         <v>110253</v>
       </c>
-      <c r="B599" s="52">
+      <c r="B604" s="52">
         <v>10101</v>
       </c>
-      <c r="C599" s="53" t="inlineStr">
+      <c r="C604" s="53" t="inlineStr">
         <is>
           <t>CIUDAD IXTEPEC</t>
         </is>
       </c>
-      <c r="D599" s="57">
+      <c r="D604" s="57">
         <v>264</v>
       </c>
-      <c r="E599" s="57">
+      <c r="E604" s="57">
         <v>456</v>
       </c>
-      <c r="F599" s="10">
-        <f>E599*0.666*24/72</f>
-      </c>
-      <c r="G599" s="54">
-        <v>0</v>
-      </c>
-      <c r="H599" s="54">
-        <v>0</v>
-      </c>
-      <c r="I599" s="54">
-        <v>0</v>
-      </c>
-      <c r="J599" s="54">
-        <v>0</v>
-      </c>
-      <c r="K599" s="54">
-        <v>0</v>
-      </c>
-      <c r="L599" s="55">
-        <v>0</v>
-      </c>
-      <c r="M599" s="54">
-        <v>0</v>
-      </c>
-      <c r="N599" s="55">
-        <v>0</v>
-      </c>
-      <c r="O599" s="10">
-        <v>0</v>
-      </c>
-      <c r="P599" s="54"/>
-      <c r="Q599" s="56">
-        <f>+P599</f>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" s="1">
+      <c r="F604" s="10">
+        <f>E604*0.666*24/72</f>
+      </c>
+      <c r="G604" s="54">
+        <v>0</v>
+      </c>
+      <c r="H604" s="54">
+        <v>0</v>
+      </c>
+      <c r="I604" s="54">
+        <v>0</v>
+      </c>
+      <c r="J604" s="54">
+        <v>0</v>
+      </c>
+      <c r="K604" s="54">
+        <v>0</v>
+      </c>
+      <c r="L604" s="55">
+        <v>0</v>
+      </c>
+      <c r="M604" s="54">
+        <v>0</v>
+      </c>
+      <c r="N604" s="55">
+        <v>0</v>
+      </c>
+      <c r="O604" s="10">
+        <v>0</v>
+      </c>
+      <c r="P604" s="54"/>
+      <c r="Q604" s="56">
+        <f>+P604</f>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1">
         <v>120203</v>
       </c>
-      <c r="B600" s="52">
+      <c r="B605" s="52">
         <v>10101</v>
       </c>
-      <c r="C600" s="53" t="inlineStr">
+      <c r="C605" s="53" t="inlineStr">
         <is>
           <t>SAN MIGUEL SOYALTEPEC</t>
         </is>
       </c>
-      <c r="D600" s="57">
+      <c r="D605" s="57">
         <v>159</v>
       </c>
-      <c r="E600" s="57">
+      <c r="E605" s="57">
         <v>291</v>
       </c>
-      <c r="F600" s="10">
-        <f>E600*0.666*24/72</f>
-      </c>
-      <c r="G600" s="54">
-        <v>0</v>
-      </c>
-      <c r="H600" s="54">
-        <v>0</v>
-      </c>
-      <c r="I600" s="54">
-        <v>0</v>
-      </c>
-      <c r="J600" s="54">
-        <v>0</v>
-      </c>
-      <c r="K600" s="54">
-        <v>0</v>
-      </c>
-      <c r="L600" s="55">
-        <v>0</v>
-      </c>
-      <c r="M600" s="54">
-        <v>0</v>
-      </c>
-      <c r="N600" s="55">
-        <v>0</v>
-      </c>
-      <c r="O600" s="10">
-        <v>0</v>
-      </c>
-      <c r="P600" s="54"/>
-      <c r="Q600" s="56">
-        <f>+P600</f>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" s="1">
+      <c r="F605" s="10">
+        <f>E605*0.666*24/72</f>
+      </c>
+      <c r="G605" s="54">
+        <v>0</v>
+      </c>
+      <c r="H605" s="54">
+        <v>0</v>
+      </c>
+      <c r="I605" s="54">
+        <v>0</v>
+      </c>
+      <c r="J605" s="54">
+        <v>0</v>
+      </c>
+      <c r="K605" s="54">
+        <v>0</v>
+      </c>
+      <c r="L605" s="55">
+        <v>0</v>
+      </c>
+      <c r="M605" s="54">
+        <v>0</v>
+      </c>
+      <c r="N605" s="55">
+        <v>0</v>
+      </c>
+      <c r="O605" s="10">
+        <v>0</v>
+      </c>
+      <c r="P605" s="54"/>
+      <c r="Q605" s="56">
+        <f>+P605</f>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1">
         <v>120389</v>
       </c>
-      <c r="B601" s="52">
+      <c r="B606" s="52">
         <v>10101</v>
       </c>
-      <c r="C601" s="53" t="inlineStr">
+      <c r="C606" s="53" t="inlineStr">
         <is>
           <t>COLONIA MARIA EUGENIA</t>
         </is>
       </c>
-      <c r="D601" s="57">
+      <c r="D606" s="57">
         <v>104</v>
       </c>
-      <c r="E601" s="57">
+      <c r="E606" s="57">
         <v>156</v>
       </c>
-      <c r="F601" s="10">
-        <f>E601*0.666*24/72</f>
-      </c>
-      <c r="G601" s="54">
-        <v>0</v>
-      </c>
-      <c r="H601" s="54">
-        <v>0</v>
-      </c>
-      <c r="I601" s="54">
-        <v>0</v>
-      </c>
-      <c r="J601" s="54">
-        <v>0</v>
-      </c>
-      <c r="K601" s="54">
-        <v>0</v>
-      </c>
-      <c r="L601" s="55">
-        <v>0</v>
-      </c>
-      <c r="M601" s="54">
-        <v>0</v>
-      </c>
-      <c r="N601" s="55">
-        <v>0</v>
-      </c>
-      <c r="O601" s="10">
-        <v>0</v>
-      </c>
-      <c r="P601" s="54"/>
-      <c r="Q601" s="56">
-        <f>+P601</f>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" s="1">
+      <c r="F606" s="10">
+        <f>E606*0.666*24/72</f>
+      </c>
+      <c r="G606" s="54">
+        <v>0</v>
+      </c>
+      <c r="H606" s="54">
+        <v>0</v>
+      </c>
+      <c r="I606" s="54">
+        <v>0</v>
+      </c>
+      <c r="J606" s="54">
+        <v>0</v>
+      </c>
+      <c r="K606" s="54">
+        <v>0</v>
+      </c>
+      <c r="L606" s="55">
+        <v>0</v>
+      </c>
+      <c r="M606" s="54">
+        <v>0</v>
+      </c>
+      <c r="N606" s="55">
+        <v>0</v>
+      </c>
+      <c r="O606" s="10">
+        <v>0</v>
+      </c>
+      <c r="P606" s="54"/>
+      <c r="Q606" s="56">
+        <f>+P606</f>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1">
         <v>120434</v>
       </c>
-      <c r="B602" s="52">
+      <c r="B607" s="52">
         <v>10101</v>
       </c>
-      <c r="C602" s="53" t="inlineStr">
+      <c r="C607" s="53" t="inlineStr">
         <is>
           <t>COLONIA OBRERA BENITO JUAREZ</t>
         </is>
       </c>
-      <c r="D602" s="57">
+      <c r="D607" s="57">
         <v>125</v>
       </c>
-      <c r="E602" s="57">
+      <c r="E607" s="57">
         <v>238</v>
       </c>
-      <c r="F602" s="10">
-        <f>E602*0.666*24/72</f>
-      </c>
-      <c r="G602" s="54">
-        <v>0</v>
-      </c>
-      <c r="H602" s="54">
-        <v>0</v>
-      </c>
-      <c r="I602" s="54">
-        <v>0</v>
-      </c>
-      <c r="J602" s="54">
-        <v>0</v>
-      </c>
-      <c r="K602" s="54">
-        <v>0</v>
-      </c>
-      <c r="L602" s="55">
-        <v>0</v>
-      </c>
-      <c r="M602" s="54">
-        <v>0</v>
-      </c>
-      <c r="N602" s="55">
-        <v>0</v>
-      </c>
-      <c r="O602" s="10">
-        <v>0</v>
-      </c>
-      <c r="P602" s="54"/>
-      <c r="Q602" s="56">
-        <f>+P602</f>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" s="1">
+      <c r="F607" s="10">
+        <f>E607*0.666*24/72</f>
+      </c>
+      <c r="G607" s="54">
+        <v>0</v>
+      </c>
+      <c r="H607" s="54">
+        <v>0</v>
+      </c>
+      <c r="I607" s="54">
+        <v>0</v>
+      </c>
+      <c r="J607" s="54">
+        <v>0</v>
+      </c>
+      <c r="K607" s="54">
+        <v>0</v>
+      </c>
+      <c r="L607" s="55">
+        <v>0</v>
+      </c>
+      <c r="M607" s="54">
+        <v>0</v>
+      </c>
+      <c r="N607" s="55">
+        <v>0</v>
+      </c>
+      <c r="O607" s="10">
+        <v>0</v>
+      </c>
+      <c r="P607" s="54"/>
+      <c r="Q607" s="56">
+        <f>+P607</f>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1">
         <v>120558</v>
       </c>
-      <c r="B603" s="52">
+      <c r="B608" s="52">
         <v>10101</v>
       </c>
-      <c r="C603" s="53" t="inlineStr">
+      <c r="C608" s="53" t="inlineStr">
         <is>
           <t>PUEBLO NUEVO TUXTEPEC</t>
         </is>
       </c>
-      <c r="D603" s="57">
+      <c r="D608" s="57">
         <v>179</v>
       </c>
-      <c r="E603" s="57">
+      <c r="E608" s="57">
         <v>284</v>
       </c>
-      <c r="F603" s="10">
-        <f>E603*0.666*24/72</f>
-      </c>
-      <c r="G603" s="54">
-        <v>0</v>
-      </c>
-      <c r="H603" s="54">
-        <v>0</v>
-      </c>
-      <c r="I603" s="54">
-        <v>0</v>
-      </c>
-      <c r="J603" s="54">
-        <v>0</v>
-      </c>
-      <c r="K603" s="54">
-        <v>0</v>
-      </c>
-      <c r="L603" s="55">
-        <v>0</v>
-      </c>
-      <c r="M603" s="54">
-        <v>0</v>
-      </c>
-      <c r="N603" s="55">
-        <v>0</v>
-      </c>
-      <c r="O603" s="10">
-        <v>0</v>
-      </c>
-      <c r="P603" s="54"/>
-      <c r="Q603" s="56">
-        <f>+P603</f>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" s="1">
+      <c r="F608" s="10">
+        <f>E608*0.666*24/72</f>
+      </c>
+      <c r="G608" s="54">
+        <v>0</v>
+      </c>
+      <c r="H608" s="54">
+        <v>0</v>
+      </c>
+      <c r="I608" s="54">
+        <v>0</v>
+      </c>
+      <c r="J608" s="54">
+        <v>0</v>
+      </c>
+      <c r="K608" s="54">
+        <v>0</v>
+      </c>
+      <c r="L608" s="55">
+        <v>0</v>
+      </c>
+      <c r="M608" s="54">
+        <v>0</v>
+      </c>
+      <c r="N608" s="55">
+        <v>0</v>
+      </c>
+      <c r="O608" s="10">
+        <v>0</v>
+      </c>
+      <c r="P608" s="54"/>
+      <c r="Q608" s="56">
+        <f>+P608</f>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1">
         <v>120563</v>
       </c>
-      <c r="B604" s="52">
+      <c r="B609" s="52">
         <v>10101</v>
       </c>
-      <c r="C604" s="53" t="inlineStr">
+      <c r="C609" s="53" t="inlineStr">
         <is>
           <t>COLONIA OAXAQUE A  LOMA BONITA</t>
         </is>
       </c>
-      <c r="D604" s="57">
+      <c r="D609" s="57">
         <v>198</v>
       </c>
-      <c r="E604" s="57">
+      <c r="E609" s="57">
         <v>358</v>
       </c>
-      <c r="F604" s="10">
-        <f>E604*0.666*24/72</f>
-      </c>
-      <c r="G604" s="54">
-        <v>0</v>
-      </c>
-      <c r="H604" s="54">
-        <v>0</v>
-      </c>
-      <c r="I604" s="54">
-        <v>0</v>
-      </c>
-      <c r="J604" s="54">
-        <v>0</v>
-      </c>
-      <c r="K604" s="54">
-        <v>0</v>
-      </c>
-      <c r="L604" s="55">
-        <v>0</v>
-      </c>
-      <c r="M604" s="54">
-        <v>0</v>
-      </c>
-      <c r="N604" s="55">
-        <v>0</v>
-      </c>
-      <c r="O604" s="10">
-        <v>0</v>
-      </c>
-      <c r="P604" s="54"/>
-      <c r="Q604" s="56">
-        <f>+P604</f>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" s="1">
+      <c r="F609" s="10">
+        <f>E609*0.666*24/72</f>
+      </c>
+      <c r="G609" s="54">
+        <v>0</v>
+      </c>
+      <c r="H609" s="54">
+        <v>0</v>
+      </c>
+      <c r="I609" s="54">
+        <v>0</v>
+      </c>
+      <c r="J609" s="54">
+        <v>0</v>
+      </c>
+      <c r="K609" s="54">
+        <v>0</v>
+      </c>
+      <c r="L609" s="55">
+        <v>0</v>
+      </c>
+      <c r="M609" s="54">
+        <v>0</v>
+      </c>
+      <c r="N609" s="55">
+        <v>0</v>
+      </c>
+      <c r="O609" s="10">
+        <v>0</v>
+      </c>
+      <c r="P609" s="54"/>
+      <c r="Q609" s="56">
+        <f>+P609</f>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1">
         <v>120581</v>
       </c>
-      <c r="B605" s="52">
+      <c r="B610" s="52">
         <v>10101</v>
       </c>
-      <c r="C605" s="53" t="inlineStr">
+      <c r="C610" s="53" t="inlineStr">
         <is>
           <t>SAN JOSE CHILTEPEC</t>
         </is>
       </c>
-      <c r="D605" s="57">
+      <c r="D610" s="57">
         <v>187</v>
       </c>
-      <c r="E605" s="57">
+      <c r="E610" s="57">
         <v>337</v>
       </c>
-      <c r="F605" s="10">
-        <f>E605*0.666*24/72</f>
-      </c>
-      <c r="G605" s="54">
-        <v>0</v>
-      </c>
-      <c r="H605" s="54">
-        <v>0</v>
-      </c>
-      <c r="I605" s="54">
-        <v>0</v>
-      </c>
-      <c r="J605" s="54">
-        <v>0</v>
-      </c>
-      <c r="K605" s="54">
-        <v>0</v>
-      </c>
-      <c r="L605" s="55">
-        <v>0</v>
-      </c>
-      <c r="M605" s="54">
-        <v>0</v>
-      </c>
-      <c r="N605" s="55">
-        <v>0</v>
-      </c>
-      <c r="O605" s="10">
-        <v>0</v>
-      </c>
-      <c r="P605" s="54"/>
-      <c r="Q605" s="56">
-        <f>+P605</f>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" s="1">
+      <c r="F610" s="10">
+        <f>E610*0.666*24/72</f>
+      </c>
+      <c r="G610" s="54">
+        <v>0</v>
+      </c>
+      <c r="H610" s="54">
+        <v>0</v>
+      </c>
+      <c r="I610" s="54">
+        <v>0</v>
+      </c>
+      <c r="J610" s="54">
+        <v>0</v>
+      </c>
+      <c r="K610" s="54">
+        <v>0</v>
+      </c>
+      <c r="L610" s="55">
+        <v>0</v>
+      </c>
+      <c r="M610" s="54">
+        <v>0</v>
+      </c>
+      <c r="N610" s="55">
+        <v>0</v>
+      </c>
+      <c r="O610" s="10">
+        <v>0</v>
+      </c>
+      <c r="P610" s="54"/>
+      <c r="Q610" s="56">
+        <f>+P610</f>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1">
         <v>123104</v>
       </c>
-      <c r="B606" s="52">
+      <c r="B611" s="52">
         <v>10101</v>
       </c>
-      <c r="C606" s="53" t="inlineStr">
+      <c r="C611" s="53" t="inlineStr">
         <is>
           <t>SAN BERNARDO MIXTEPEC</t>
         </is>
       </c>
-      <c r="D606" s="57">
+      <c r="D611" s="57">
         <v>118</v>
       </c>
-      <c r="E606" s="57">
+      <c r="E611" s="57">
         <v>166</v>
       </c>
-      <c r="F606" s="10">
-        <f>E606*0.666*24/72</f>
-      </c>
-      <c r="G606" s="54">
-        <v>0</v>
-      </c>
-      <c r="H606" s="54">
-        <v>0</v>
-      </c>
-      <c r="I606" s="54">
-        <v>0</v>
-      </c>
-      <c r="J606" s="54">
-        <v>0</v>
-      </c>
-      <c r="K606" s="54">
-        <v>0</v>
-      </c>
-      <c r="L606" s="55">
-        <v>0</v>
-      </c>
-      <c r="M606" s="54">
-        <v>0</v>
-      </c>
-      <c r="N606" s="55">
-        <v>0</v>
-      </c>
-      <c r="O606" s="10">
-        <v>0</v>
-      </c>
-      <c r="P606" s="54"/>
-      <c r="Q606" s="56">
-        <f>+P606</f>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" s="1">
+      <c r="F611" s="10">
+        <f>E611*0.666*24/72</f>
+      </c>
+      <c r="G611" s="54">
+        <v>0</v>
+      </c>
+      <c r="H611" s="54">
+        <v>0</v>
+      </c>
+      <c r="I611" s="54">
+        <v>0</v>
+      </c>
+      <c r="J611" s="54">
+        <v>0</v>
+      </c>
+      <c r="K611" s="54">
+        <v>0</v>
+      </c>
+      <c r="L611" s="55">
+        <v>0</v>
+      </c>
+      <c r="M611" s="54">
+        <v>0</v>
+      </c>
+      <c r="N611" s="55">
+        <v>0</v>
+      </c>
+      <c r="O611" s="10">
+        <v>0</v>
+      </c>
+      <c r="P611" s="54"/>
+      <c r="Q611" s="56">
+        <f>+P611</f>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1">
         <v>184102</v>
       </c>
-      <c r="B607" s="52">
+      <c r="B612" s="52">
         <v>10101</v>
       </c>
-      <c r="C607" s="53" t="inlineStr">
+      <c r="C612" s="53" t="inlineStr">
         <is>
           <t>COL  EL PROGRESO</t>
         </is>
       </c>
-      <c r="D607" s="57">
+      <c r="D612" s="57">
         <v>89</v>
       </c>
-      <c r="E607" s="57">
+      <c r="E612" s="57">
         <v>176</v>
       </c>
-      <c r="F607" s="10">
-        <f>E607*0.666*24/72</f>
-      </c>
-      <c r="G607" s="54">
-        <v>0</v>
-      </c>
-      <c r="H607" s="54">
-        <v>0</v>
-      </c>
-      <c r="I607" s="54">
-        <v>0</v>
-      </c>
-      <c r="J607" s="54">
-        <v>0</v>
-      </c>
-      <c r="K607" s="54">
-        <v>0</v>
-      </c>
-      <c r="L607" s="55">
-        <v>0</v>
-      </c>
-      <c r="M607" s="54">
-        <v>0</v>
-      </c>
-      <c r="N607" s="55">
-        <v>0</v>
-      </c>
-      <c r="O607" s="10">
-        <v>0</v>
-      </c>
-      <c r="P607" s="54"/>
-      <c r="Q607" s="56">
-        <f>+P607</f>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" s="1">
+      <c r="F612" s="10">
+        <f>E612*0.666*24/72</f>
+      </c>
+      <c r="G612" s="54">
+        <v>0</v>
+      </c>
+      <c r="H612" s="54">
+        <v>0</v>
+      </c>
+      <c r="I612" s="54">
+        <v>0</v>
+      </c>
+      <c r="J612" s="54">
+        <v>0</v>
+      </c>
+      <c r="K612" s="54">
+        <v>0</v>
+      </c>
+      <c r="L612" s="55">
+        <v>0</v>
+      </c>
+      <c r="M612" s="54">
+        <v>0</v>
+      </c>
+      <c r="N612" s="55">
+        <v>0</v>
+      </c>
+      <c r="O612" s="10">
+        <v>0</v>
+      </c>
+      <c r="P612" s="54"/>
+      <c r="Q612" s="56">
+        <f>+P612</f>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1">
         <v>184103</v>
       </c>
-      <c r="B608" s="52">
+      <c r="B613" s="52">
         <v>10101</v>
       </c>
-      <c r="C608" s="53" t="inlineStr">
+      <c r="C613" s="53" t="inlineStr">
         <is>
           <t>BENITO JUAREZ (LAS LIMAS)</t>
         </is>
       </c>
-      <c r="D608" s="57">
+      <c r="D613" s="57">
         <v>147</v>
       </c>
-      <c r="E608" s="57">
+      <c r="E613" s="57">
         <v>260</v>
       </c>
-      <c r="F608" s="10">
-        <f>E608*0.666*24/72</f>
-      </c>
-      <c r="G608" s="54">
-        <v>0</v>
-      </c>
-      <c r="H608" s="54">
-        <v>0</v>
-      </c>
-      <c r="I608" s="54">
-        <v>0</v>
-      </c>
-      <c r="J608" s="54">
-        <v>0</v>
-      </c>
-      <c r="K608" s="54">
-        <v>0</v>
-      </c>
-      <c r="L608" s="55">
-        <v>0</v>
-      </c>
-      <c r="M608" s="54">
-        <v>0</v>
-      </c>
-      <c r="N608" s="55">
-        <v>0</v>
-      </c>
-      <c r="O608" s="10">
-        <v>0</v>
-      </c>
-      <c r="P608" s="54"/>
-      <c r="Q608" s="56">
-        <f>+P608</f>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" s="1">
+      <c r="F613" s="10">
+        <f>E613*0.666*24/72</f>
+      </c>
+      <c r="G613" s="54">
+        <v>0</v>
+      </c>
+      <c r="H613" s="54">
+        <v>0</v>
+      </c>
+      <c r="I613" s="54">
+        <v>0</v>
+      </c>
+      <c r="J613" s="54">
+        <v>0</v>
+      </c>
+      <c r="K613" s="54">
+        <v>0</v>
+      </c>
+      <c r="L613" s="55">
+        <v>0</v>
+      </c>
+      <c r="M613" s="54">
+        <v>0</v>
+      </c>
+      <c r="N613" s="55">
+        <v>0</v>
+      </c>
+      <c r="O613" s="10">
+        <v>0</v>
+      </c>
+      <c r="P613" s="54"/>
+      <c r="Q613" s="56">
+        <f>+P613</f>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1">
         <v>184104</v>
       </c>
-      <c r="B609" s="52">
+      <c r="B614" s="52">
         <v>10101</v>
       </c>
-      <c r="C609" s="53" t="inlineStr">
+      <c r="C614" s="53" t="inlineStr">
         <is>
           <t>LA MODERNA</t>
         </is>
       </c>
-      <c r="D609" s="57">
+      <c r="D614" s="57">
         <v>72</v>
       </c>
-      <c r="E609" s="57">
+      <c r="E614" s="57">
         <v>157</v>
       </c>
-      <c r="F609" s="10">
-        <f>E609*0.666*24/72</f>
-      </c>
-      <c r="G609" s="54">
-        <v>0</v>
-      </c>
-      <c r="H609" s="54">
-        <v>0</v>
-      </c>
-      <c r="I609" s="54">
-        <v>0</v>
-      </c>
-      <c r="J609" s="54">
-        <v>0</v>
-      </c>
-      <c r="K609" s="54">
-        <v>0</v>
-      </c>
-      <c r="L609" s="55">
-        <v>0</v>
-      </c>
-      <c r="M609" s="54">
-        <v>0</v>
-      </c>
-      <c r="N609" s="55">
-        <v>0</v>
-      </c>
-      <c r="O609" s="10">
-        <v>0</v>
-      </c>
-      <c r="P609" s="54"/>
-      <c r="Q609" s="56">
-        <f>+P609</f>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" s="1">
+      <c r="F614" s="10">
+        <f>E614*0.666*24/72</f>
+      </c>
+      <c r="G614" s="54">
+        <v>0</v>
+      </c>
+      <c r="H614" s="54">
+        <v>0</v>
+      </c>
+      <c r="I614" s="54">
+        <v>0</v>
+      </c>
+      <c r="J614" s="54">
+        <v>0</v>
+      </c>
+      <c r="K614" s="54">
+        <v>0</v>
+      </c>
+      <c r="L614" s="55">
+        <v>0</v>
+      </c>
+      <c r="M614" s="54">
+        <v>0</v>
+      </c>
+      <c r="N614" s="55">
+        <v>0</v>
+      </c>
+      <c r="O614" s="10">
+        <v>0</v>
+      </c>
+      <c r="P614" s="54"/>
+      <c r="Q614" s="56">
+        <f>+P614</f>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1">
         <v>184106</v>
       </c>
-      <c r="B610" s="52">
+      <c r="B615" s="52">
         <v>10101</v>
       </c>
-      <c r="C610" s="53" t="inlineStr">
+      <c r="C615" s="53" t="inlineStr">
         <is>
           <t>SAN BARTOLO</t>
         </is>
       </c>
-      <c r="D610" s="57">
+      <c r="D615" s="57">
         <v>156</v>
       </c>
-      <c r="E610" s="57">
+      <c r="E615" s="57">
         <v>259</v>
       </c>
-      <c r="F610" s="10">
-        <f>E610*0.666*24/72</f>
-      </c>
-      <c r="G610" s="54">
-        <v>0</v>
-      </c>
-      <c r="H610" s="54">
-        <v>0</v>
-      </c>
-      <c r="I610" s="54">
-        <v>0</v>
-      </c>
-      <c r="J610" s="54">
-        <v>0</v>
-      </c>
-      <c r="K610" s="54">
-        <v>0</v>
-      </c>
-      <c r="L610" s="55">
-        <v>0</v>
-      </c>
-      <c r="M610" s="54">
-        <v>0</v>
-      </c>
-      <c r="N610" s="55">
-        <v>0</v>
-      </c>
-      <c r="O610" s="10">
-        <v>0</v>
-      </c>
-      <c r="P610" s="54"/>
-      <c r="Q610" s="56">
-        <f>+P610</f>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" s="1">
+      <c r="F615" s="10">
+        <f>E615*0.666*24/72</f>
+      </c>
+      <c r="G615" s="54">
+        <v>0</v>
+      </c>
+      <c r="H615" s="54">
+        <v>0</v>
+      </c>
+      <c r="I615" s="54">
+        <v>0</v>
+      </c>
+      <c r="J615" s="54">
+        <v>0</v>
+      </c>
+      <c r="K615" s="54">
+        <v>0</v>
+      </c>
+      <c r="L615" s="55">
+        <v>0</v>
+      </c>
+      <c r="M615" s="54">
+        <v>0</v>
+      </c>
+      <c r="N615" s="55">
+        <v>0</v>
+      </c>
+      <c r="O615" s="10">
+        <v>0</v>
+      </c>
+      <c r="P615" s="54"/>
+      <c r="Q615" s="56">
+        <f>+P615</f>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1">
         <v>184107</v>
       </c>
-      <c r="B611" s="52">
+      <c r="B616" s="52">
         <v>10101</v>
       </c>
-      <c r="C611" s="53" t="inlineStr">
+      <c r="C616" s="53" t="inlineStr">
         <is>
           <t>PAPALOAPAM</t>
         </is>
       </c>
-      <c r="D611" s="57">
+      <c r="D616" s="57">
         <v>150</v>
       </c>
-      <c r="E611" s="57">
+      <c r="E616" s="57">
         <v>269</v>
       </c>
-      <c r="F611" s="10">
-        <f>E611*0.666*24/72</f>
-      </c>
-      <c r="G611" s="54">
-        <v>0</v>
-      </c>
-      <c r="H611" s="54">
-        <v>0</v>
-      </c>
-      <c r="I611" s="54">
-        <v>0</v>
-      </c>
-      <c r="J611" s="54">
-        <v>0</v>
-      </c>
-      <c r="K611" s="54">
-        <v>0</v>
-      </c>
-      <c r="L611" s="55">
-        <v>0</v>
-      </c>
-      <c r="M611" s="54">
-        <v>0</v>
-      </c>
-      <c r="N611" s="55">
-        <v>0</v>
-      </c>
-      <c r="O611" s="10">
-        <v>0</v>
-      </c>
-      <c r="P611" s="54"/>
-      <c r="Q611" s="56">
-        <f>+P611</f>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" s="1">
+      <c r="F616" s="10">
+        <f>E616*0.666*24/72</f>
+      </c>
+      <c r="G616" s="54">
+        <v>0</v>
+      </c>
+      <c r="H616" s="54">
+        <v>0</v>
+      </c>
+      <c r="I616" s="54">
+        <v>0</v>
+      </c>
+      <c r="J616" s="54">
+        <v>0</v>
+      </c>
+      <c r="K616" s="54">
+        <v>0</v>
+      </c>
+      <c r="L616" s="55">
+        <v>0</v>
+      </c>
+      <c r="M616" s="54">
+        <v>0</v>
+      </c>
+      <c r="N616" s="55">
+        <v>0</v>
+      </c>
+      <c r="O616" s="10">
+        <v>0</v>
+      </c>
+      <c r="P616" s="54"/>
+      <c r="Q616" s="56">
+        <f>+P616</f>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1">
         <v>184108</v>
       </c>
-      <c r="B612" s="52">
+      <c r="B617" s="52">
         <v>10101</v>
       </c>
-      <c r="C612" s="53" t="inlineStr">
+      <c r="C617" s="53" t="inlineStr">
         <is>
           <t>CAMELIA ROJA</t>
         </is>
       </c>
-      <c r="D612" s="57">
+      <c r="D617" s="57">
         <v>86</v>
       </c>
-      <c r="E612" s="57">
+      <c r="E617" s="57">
         <v>140</v>
       </c>
-      <c r="F612" s="10">
-        <f>E612*0.666*24/72</f>
-      </c>
-      <c r="G612" s="54">
-        <v>0</v>
-      </c>
-      <c r="H612" s="54">
-        <v>0</v>
-      </c>
-      <c r="I612" s="54">
-        <v>0</v>
-      </c>
-      <c r="J612" s="54">
-        <v>0</v>
-      </c>
-      <c r="K612" s="54">
-        <v>0</v>
-      </c>
-      <c r="L612" s="55">
-        <v>0</v>
-      </c>
-      <c r="M612" s="54">
-        <v>0</v>
-      </c>
-      <c r="N612" s="55">
-        <v>0</v>
-      </c>
-      <c r="O612" s="10">
-        <v>0</v>
-      </c>
-      <c r="P612" s="54"/>
-      <c r="Q612" s="56">
-        <f>+P612</f>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" s="1">
+      <c r="F617" s="10">
+        <f>E617*0.666*24/72</f>
+      </c>
+      <c r="G617" s="54">
+        <v>0</v>
+      </c>
+      <c r="H617" s="54">
+        <v>0</v>
+      </c>
+      <c r="I617" s="54">
+        <v>0</v>
+      </c>
+      <c r="J617" s="54">
+        <v>0</v>
+      </c>
+      <c r="K617" s="54">
+        <v>0</v>
+      </c>
+      <c r="L617" s="55">
+        <v>0</v>
+      </c>
+      <c r="M617" s="54">
+        <v>0</v>
+      </c>
+      <c r="N617" s="55">
+        <v>0</v>
+      </c>
+      <c r="O617" s="10">
+        <v>0</v>
+      </c>
+      <c r="P617" s="54"/>
+      <c r="Q617" s="56">
+        <f>+P617</f>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1">
         <v>184109</v>
       </c>
-      <c r="B613" s="52">
+      <c r="B618" s="52">
         <v>10101</v>
       </c>
-      <c r="C613" s="53" t="inlineStr">
+      <c r="C618" s="53" t="inlineStr">
         <is>
           <t>COL  HIDALGO</t>
         </is>
       </c>
-      <c r="D613" s="57">
+      <c r="D618" s="57">
         <v>223</v>
       </c>
-      <c r="E613" s="57">
+      <c r="E618" s="57">
         <v>365</v>
       </c>
-      <c r="F613" s="10">
-        <f>E613*0.666*24/72</f>
-      </c>
-      <c r="G613" s="54">
-        <v>0</v>
-      </c>
-      <c r="H613" s="54">
-        <v>0</v>
-      </c>
-      <c r="I613" s="54">
-        <v>0</v>
-      </c>
-      <c r="J613" s="54">
-        <v>0</v>
-      </c>
-      <c r="K613" s="54">
-        <v>0</v>
-      </c>
-      <c r="L613" s="55">
-        <v>0</v>
-      </c>
-      <c r="M613" s="54">
-        <v>0</v>
-      </c>
-      <c r="N613" s="55">
-        <v>0</v>
-      </c>
-      <c r="O613" s="10">
-        <v>0</v>
-      </c>
-      <c r="P613" s="54"/>
-      <c r="Q613" s="56">
-        <f>+P613</f>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" s="1">
+      <c r="F618" s="10">
+        <f>E618*0.666*24/72</f>
+      </c>
+      <c r="G618" s="54">
+        <v>0</v>
+      </c>
+      <c r="H618" s="54">
+        <v>0</v>
+      </c>
+      <c r="I618" s="54">
+        <v>0</v>
+      </c>
+      <c r="J618" s="54">
+        <v>0</v>
+      </c>
+      <c r="K618" s="54">
+        <v>0</v>
+      </c>
+      <c r="L618" s="55">
+        <v>0</v>
+      </c>
+      <c r="M618" s="54">
+        <v>0</v>
+      </c>
+      <c r="N618" s="55">
+        <v>0</v>
+      </c>
+      <c r="O618" s="10">
+        <v>0</v>
+      </c>
+      <c r="P618" s="54"/>
+      <c r="Q618" s="56">
+        <f>+P618</f>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1">
         <v>184112</v>
       </c>
-      <c r="B614" s="52">
+      <c r="B619" s="52">
         <v>10101</v>
       </c>
-      <c r="C614" s="53" t="inlineStr">
+      <c r="C619" s="53" t="inlineStr">
         <is>
           <t>SURESTE 2A  ETAPA</t>
         </is>
       </c>
-      <c r="D614" s="57">
+      <c r="D619" s="57">
         <v>112</v>
       </c>
-      <c r="E614" s="57">
+      <c r="E619" s="57">
         <v>223</v>
       </c>
-      <c r="F614" s="10">
-        <f>E614*0.666*24/72</f>
-      </c>
-      <c r="G614" s="54">
-        <v>0</v>
-      </c>
-      <c r="H614" s="54">
-        <v>0</v>
-      </c>
-      <c r="I614" s="54">
-        <v>0</v>
-      </c>
-      <c r="J614" s="54">
-        <v>0</v>
-      </c>
-      <c r="K614" s="54">
-        <v>0</v>
-      </c>
-      <c r="L614" s="55">
-        <v>0</v>
-      </c>
-      <c r="M614" s="54">
-        <v>0</v>
-      </c>
-      <c r="N614" s="55">
-        <v>0</v>
-      </c>
-      <c r="O614" s="10">
-        <v>0</v>
-      </c>
-      <c r="P614" s="54"/>
-      <c r="Q614" s="56">
-        <f>+P614</f>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" s="1">
+      <c r="F619" s="10">
+        <f>E619*0.666*24/72</f>
+      </c>
+      <c r="G619" s="54">
+        <v>0</v>
+      </c>
+      <c r="H619" s="54">
+        <v>0</v>
+      </c>
+      <c r="I619" s="54">
+        <v>0</v>
+      </c>
+      <c r="J619" s="54">
+        <v>0</v>
+      </c>
+      <c r="K619" s="54">
+        <v>0</v>
+      </c>
+      <c r="L619" s="55">
+        <v>0</v>
+      </c>
+      <c r="M619" s="54">
+        <v>0</v>
+      </c>
+      <c r="N619" s="55">
+        <v>0</v>
+      </c>
+      <c r="O619" s="10">
+        <v>0</v>
+      </c>
+      <c r="P619" s="54"/>
+      <c r="Q619" s="56">
+        <f>+P619</f>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1">
         <v>184116</v>
       </c>
-      <c r="B615" s="52">
+      <c r="B620" s="52">
         <v>10101</v>
       </c>
-      <c r="C615" s="53" t="inlineStr">
+      <c r="C620" s="53" t="inlineStr">
         <is>
           <t>BENEMERITO JUAREZ</t>
         </is>
       </c>
-      <c r="D615" s="57">
+      <c r="D620" s="57">
         <v>119</v>
       </c>
-      <c r="E615" s="57">
+      <c r="E620" s="57">
         <v>177</v>
-      </c>
-      <c r="F615" s="10">
-        <f>E615*0.666*24/72</f>
-      </c>
-      <c r="G615" s="54">
-        <v>0</v>
-      </c>
-      <c r="H615" s="54">
-        <v>0</v>
-      </c>
-      <c r="I615" s="54">
-        <v>0</v>
-      </c>
-      <c r="J615" s="54">
-        <v>0</v>
-      </c>
-      <c r="K615" s="54">
-        <v>0</v>
-      </c>
-      <c r="L615" s="55">
-        <v>0</v>
-      </c>
-      <c r="M615" s="54">
-        <v>0</v>
-      </c>
-      <c r="N615" s="55">
-        <v>0</v>
-      </c>
-      <c r="O615" s="10">
-        <v>0</v>
-      </c>
-      <c r="P615" s="54"/>
-      <c r="Q615" s="56">
-        <f>+P615</f>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" s="1">
-        <v>184129</v>
-      </c>
-      <c r="B616" s="52">
-        <v>10101</v>
-      </c>
-      <c r="C616" s="53" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA TUXTEPEC</t>
-        </is>
-      </c>
-      <c r="D616" s="57">
-        <v>77</v>
-      </c>
-      <c r="E616" s="57">
-        <v>156</v>
-      </c>
-      <c r="F616" s="10">
-        <f>E616*0.666*24/72</f>
-      </c>
-      <c r="G616" s="54">
-        <v>0</v>
-      </c>
-      <c r="H616" s="54">
-        <v>0</v>
-      </c>
-      <c r="I616" s="54">
-        <v>0</v>
-      </c>
-      <c r="J616" s="54">
-        <v>0</v>
-      </c>
-      <c r="K616" s="54">
-        <v>0</v>
-      </c>
-      <c r="L616" s="55">
-        <v>0</v>
-      </c>
-      <c r="M616" s="54">
-        <v>0</v>
-      </c>
-      <c r="N616" s="55">
-        <v>0</v>
-      </c>
-      <c r="O616" s="10">
-        <v>0</v>
-      </c>
-      <c r="P616" s="54"/>
-      <c r="Q616" s="56">
-        <f>+P616</f>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" s="1">
-        <v>184151</v>
-      </c>
-      <c r="B617" s="52">
-        <v>10101</v>
-      </c>
-      <c r="C617" s="53" t="inlineStr">
-        <is>
-          <t>EL PARAISO</t>
-        </is>
-      </c>
-      <c r="D617" s="57">
-        <v>66</v>
-      </c>
-      <c r="E617" s="57">
-        <v>109</v>
-      </c>
-      <c r="F617" s="10">
-        <f>E617*0.666*24/72</f>
-      </c>
-      <c r="G617" s="54">
-        <v>0</v>
-      </c>
-      <c r="H617" s="54">
-        <v>0</v>
-      </c>
-      <c r="I617" s="54">
-        <v>0</v>
-      </c>
-      <c r="J617" s="54">
-        <v>0</v>
-      </c>
-      <c r="K617" s="54">
-        <v>0</v>
-      </c>
-      <c r="L617" s="55">
-        <v>0</v>
-      </c>
-      <c r="M617" s="54">
-        <v>0</v>
-      </c>
-      <c r="N617" s="55">
-        <v>0</v>
-      </c>
-      <c r="O617" s="10">
-        <v>0</v>
-      </c>
-      <c r="P617" s="54"/>
-      <c r="Q617" s="56">
-        <f>+P617</f>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" s="1">
-        <v>184166</v>
-      </c>
-      <c r="B618" s="52">
-        <v>10101</v>
-      </c>
-      <c r="C618" s="53" t="inlineStr">
-        <is>
-          <t>COL. 23 DE NOVIEMBRE</t>
-        </is>
-      </c>
-      <c r="D618" s="57">
-        <v>137</v>
-      </c>
-      <c r="E618" s="57">
-        <v>244</v>
-      </c>
-      <c r="F618" s="10">
-        <f>E618*0.666*24/72</f>
-      </c>
-      <c r="G618" s="54">
-        <v>0</v>
-      </c>
-      <c r="H618" s="54">
-        <v>0</v>
-      </c>
-      <c r="I618" s="54">
-        <v>0</v>
-      </c>
-      <c r="J618" s="54">
-        <v>0</v>
-      </c>
-      <c r="K618" s="54">
-        <v>0</v>
-      </c>
-      <c r="L618" s="55">
-        <v>0</v>
-      </c>
-      <c r="M618" s="54">
-        <v>0</v>
-      </c>
-      <c r="N618" s="55">
-        <v>0</v>
-      </c>
-      <c r="O618" s="10">
-        <v>0</v>
-      </c>
-      <c r="P618" s="54"/>
-      <c r="Q618" s="56">
-        <f>+P618</f>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" s="1">
-        <v>184167</v>
-      </c>
-      <c r="B619" s="52">
-        <v>10101</v>
-      </c>
-      <c r="C619" s="53" t="inlineStr">
-        <is>
-          <t>COL. DEL CASTILLO</t>
-        </is>
-      </c>
-      <c r="D619" s="57">
-        <v>122</v>
-      </c>
-      <c r="E619" s="57">
-        <v>241</v>
-      </c>
-      <c r="F619" s="10">
-        <f>E619*0.666*24/72</f>
-      </c>
-      <c r="G619" s="54">
-        <v>0</v>
-      </c>
-      <c r="H619" s="54">
-        <v>0</v>
-      </c>
-      <c r="I619" s="54">
-        <v>0</v>
-      </c>
-      <c r="J619" s="54">
-        <v>0</v>
-      </c>
-      <c r="K619" s="54">
-        <v>0</v>
-      </c>
-      <c r="L619" s="55">
-        <v>0</v>
-      </c>
-      <c r="M619" s="54">
-        <v>0</v>
-      </c>
-      <c r="N619" s="55">
-        <v>0</v>
-      </c>
-      <c r="O619" s="10">
-        <v>0</v>
-      </c>
-      <c r="P619" s="54"/>
-      <c r="Q619" s="56">
-        <f>+P619</f>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" s="1">
-        <v>184170</v>
-      </c>
-      <c r="B620" s="52">
-        <v>10101</v>
-      </c>
-      <c r="C620" s="53" t="inlineStr">
-        <is>
-          <t>SAN JUAN BAUTISTA TUXTEPEC</t>
-        </is>
-      </c>
-      <c r="D620" s="57">
-        <v>169</v>
-      </c>
-      <c r="E620" s="57">
-        <v>247</v>
       </c>
       <c r="F620" s="10">
         <f>E620*0.666*24/72</f>
@@ -70178,7 +70168,7 @@
     </row>
     <row r="621">
       <c r="A621" s="1">
-        <v>184171</v>
+        <v>184129</v>
       </c>
       <c r="B621" s="52">
         <v>10101</v>
@@ -70189,10 +70179,10 @@
         </is>
       </c>
       <c r="D621" s="57">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E621" s="57">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="F621" s="10">
         <f>E621*0.666*24/72</f>
@@ -70231,21 +70221,21 @@
     </row>
     <row r="622">
       <c r="A622" s="1">
-        <v>184172</v>
+        <v>184151</v>
       </c>
       <c r="B622" s="52">
         <v>10101</v>
       </c>
       <c r="C622" s="53" t="inlineStr">
         <is>
-          <t>VICTOR BRAVO AHUJA</t>
+          <t>EL PARAISO</t>
         </is>
       </c>
       <c r="D622" s="57">
-        <v>429</v>
+        <v>66</v>
       </c>
       <c r="E622" s="57">
-        <v>630</v>
+        <v>109</v>
       </c>
       <c r="F622" s="10">
         <f>E622*0.666*24/72</f>
@@ -70284,21 +70274,21 @@
     </row>
     <row r="623">
       <c r="A623" s="1">
-        <v>184173</v>
+        <v>184166</v>
       </c>
       <c r="B623" s="52">
         <v>10101</v>
       </c>
       <c r="C623" s="53" t="inlineStr">
         <is>
-          <t>PASO RINC N</t>
+          <t>COL. 23 DE NOVIEMBRE</t>
         </is>
       </c>
       <c r="D623" s="57">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="E623" s="57">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="F623" s="10">
         <f>E623*0.666*24/72</f>
@@ -70337,21 +70327,21 @@
     </row>
     <row r="624">
       <c r="A624" s="1">
-        <v>184174</v>
+        <v>184167</v>
       </c>
       <c r="B624" s="52">
         <v>10101</v>
       </c>
       <c r="C624" s="53" t="inlineStr">
         <is>
-          <t>GENERAL L ZARO CARDENAS</t>
+          <t>COL. DEL CASTILLO</t>
         </is>
       </c>
       <c r="D624" s="57">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="E624" s="57">
-        <v>129</v>
+        <v>241</v>
       </c>
       <c r="F624" s="10">
         <f>E624*0.666*24/72</f>
@@ -70390,7 +70380,7 @@
     </row>
     <row r="625">
       <c r="A625" s="1">
-        <v>184175</v>
+        <v>184170</v>
       </c>
       <c r="B625" s="52">
         <v>10101</v>
@@ -70401,10 +70391,10 @@
         </is>
       </c>
       <c r="D625" s="57">
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="E625" s="57">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="F625" s="10">
         <f>E625*0.666*24/72</f>
@@ -70443,989 +70433,1254 @@
     </row>
     <row r="626">
       <c r="A626" s="1">
-        <v>295103</v>
+        <v>184171</v>
       </c>
       <c r="B626" s="52">
         <v>10101</v>
       </c>
       <c r="C626" s="53" t="inlineStr">
+        <is>
+          <t>SAN JUAN BAUTISTA TUXTEPEC</t>
+        </is>
+      </c>
+      <c r="D626" s="57">
+        <v>80</v>
+      </c>
+      <c r="E626" s="57">
+        <v>126</v>
+      </c>
+      <c r="F626" s="10">
+        <f>E626*0.666*24/72</f>
+      </c>
+      <c r="G626" s="54">
+        <v>0</v>
+      </c>
+      <c r="H626" s="54">
+        <v>0</v>
+      </c>
+      <c r="I626" s="54">
+        <v>0</v>
+      </c>
+      <c r="J626" s="54">
+        <v>0</v>
+      </c>
+      <c r="K626" s="54">
+        <v>0</v>
+      </c>
+      <c r="L626" s="55">
+        <v>0</v>
+      </c>
+      <c r="M626" s="54">
+        <v>0</v>
+      </c>
+      <c r="N626" s="55">
+        <v>0</v>
+      </c>
+      <c r="O626" s="10">
+        <v>0</v>
+      </c>
+      <c r="P626" s="54"/>
+      <c r="Q626" s="56">
+        <f>+P626</f>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1">
+        <v>184172</v>
+      </c>
+      <c r="B627" s="52">
+        <v>10101</v>
+      </c>
+      <c r="C627" s="53" t="inlineStr">
+        <is>
+          <t>VICTOR BRAVO AHUJA</t>
+        </is>
+      </c>
+      <c r="D627" s="57">
+        <v>429</v>
+      </c>
+      <c r="E627" s="57">
+        <v>630</v>
+      </c>
+      <c r="F627" s="10">
+        <f>E627*0.666*24/72</f>
+      </c>
+      <c r="G627" s="54">
+        <v>0</v>
+      </c>
+      <c r="H627" s="54">
+        <v>0</v>
+      </c>
+      <c r="I627" s="54">
+        <v>0</v>
+      </c>
+      <c r="J627" s="54">
+        <v>0</v>
+      </c>
+      <c r="K627" s="54">
+        <v>0</v>
+      </c>
+      <c r="L627" s="55">
+        <v>0</v>
+      </c>
+      <c r="M627" s="54">
+        <v>0</v>
+      </c>
+      <c r="N627" s="55">
+        <v>0</v>
+      </c>
+      <c r="O627" s="10">
+        <v>0</v>
+      </c>
+      <c r="P627" s="54"/>
+      <c r="Q627" s="56">
+        <f>+P627</f>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1">
+        <v>184173</v>
+      </c>
+      <c r="B628" s="52">
+        <v>10101</v>
+      </c>
+      <c r="C628" s="53" t="inlineStr">
+        <is>
+          <t>PASO RINC N</t>
+        </is>
+      </c>
+      <c r="D628" s="57">
+        <v>89</v>
+      </c>
+      <c r="E628" s="57">
+        <v>152</v>
+      </c>
+      <c r="F628" s="10">
+        <f>E628*0.666*24/72</f>
+      </c>
+      <c r="G628" s="54">
+        <v>0</v>
+      </c>
+      <c r="H628" s="54">
+        <v>0</v>
+      </c>
+      <c r="I628" s="54">
+        <v>0</v>
+      </c>
+      <c r="J628" s="54">
+        <v>0</v>
+      </c>
+      <c r="K628" s="54">
+        <v>0</v>
+      </c>
+      <c r="L628" s="55">
+        <v>0</v>
+      </c>
+      <c r="M628" s="54">
+        <v>0</v>
+      </c>
+      <c r="N628" s="55">
+        <v>0</v>
+      </c>
+      <c r="O628" s="10">
+        <v>0</v>
+      </c>
+      <c r="P628" s="54"/>
+      <c r="Q628" s="56">
+        <f>+P628</f>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1">
+        <v>184174</v>
+      </c>
+      <c r="B629" s="52">
+        <v>10101</v>
+      </c>
+      <c r="C629" s="53" t="inlineStr">
+        <is>
+          <t>GENERAL L ZARO CARDENAS</t>
+        </is>
+      </c>
+      <c r="D629" s="57">
+        <v>69</v>
+      </c>
+      <c r="E629" s="57">
+        <v>129</v>
+      </c>
+      <c r="F629" s="10">
+        <f>E629*0.666*24/72</f>
+      </c>
+      <c r="G629" s="54">
+        <v>0</v>
+      </c>
+      <c r="H629" s="54">
+        <v>0</v>
+      </c>
+      <c r="I629" s="54">
+        <v>0</v>
+      </c>
+      <c r="J629" s="54">
+        <v>0</v>
+      </c>
+      <c r="K629" s="54">
+        <v>0</v>
+      </c>
+      <c r="L629" s="55">
+        <v>0</v>
+      </c>
+      <c r="M629" s="54">
+        <v>0</v>
+      </c>
+      <c r="N629" s="55">
+        <v>0</v>
+      </c>
+      <c r="O629" s="10">
+        <v>0</v>
+      </c>
+      <c r="P629" s="54"/>
+      <c r="Q629" s="56">
+        <f>+P629</f>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1">
+        <v>184175</v>
+      </c>
+      <c r="B630" s="52">
+        <v>10101</v>
+      </c>
+      <c r="C630" s="53" t="inlineStr">
+        <is>
+          <t>SAN JUAN BAUTISTA TUXTEPEC</t>
+        </is>
+      </c>
+      <c r="D630" s="57">
+        <v>83</v>
+      </c>
+      <c r="E630" s="57">
+        <v>134</v>
+      </c>
+      <c r="F630" s="10">
+        <f>E630*0.666*24/72</f>
+      </c>
+      <c r="G630" s="54">
+        <v>0</v>
+      </c>
+      <c r="H630" s="54">
+        <v>0</v>
+      </c>
+      <c r="I630" s="54">
+        <v>0</v>
+      </c>
+      <c r="J630" s="54">
+        <v>0</v>
+      </c>
+      <c r="K630" s="54">
+        <v>0</v>
+      </c>
+      <c r="L630" s="55">
+        <v>0</v>
+      </c>
+      <c r="M630" s="54">
+        <v>0</v>
+      </c>
+      <c r="N630" s="55">
+        <v>0</v>
+      </c>
+      <c r="O630" s="10">
+        <v>0</v>
+      </c>
+      <c r="P630" s="54"/>
+      <c r="Q630" s="56">
+        <f>+P630</f>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1">
+        <v>295103</v>
+      </c>
+      <c r="B631" s="52">
+        <v>10101</v>
+      </c>
+      <c r="C631" s="53" t="inlineStr">
         <is>
           <t>BARRIO SAN ANTONIO</t>
         </is>
       </c>
-      <c r="D626" s="57">
+      <c r="D631" s="57">
         <v>196</v>
       </c>
-      <c r="E626" s="57">
+      <c r="E631" s="57">
         <v>276</v>
       </c>
-      <c r="F626" s="10">
-        <f>E626*0.666*24/72</f>
-      </c>
-      <c r="G626" s="54">
-        <v>0</v>
-      </c>
-      <c r="H626" s="54">
-        <v>0</v>
-      </c>
-      <c r="I626" s="54">
-        <v>0</v>
-      </c>
-      <c r="J626" s="54">
-        <v>0</v>
-      </c>
-      <c r="K626" s="54">
-        <v>0</v>
-      </c>
-      <c r="L626" s="55">
-        <v>0</v>
-      </c>
-      <c r="M626" s="54">
-        <v>0</v>
-      </c>
-      <c r="N626" s="55">
-        <v>0</v>
-      </c>
-      <c r="O626" s="10">
-        <v>0</v>
-      </c>
-      <c r="P626" s="54"/>
-      <c r="Q626" s="56">
-        <f>+P626</f>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" s="1">
+      <c r="F631" s="10">
+        <f>E631*0.666*24/72</f>
+      </c>
+      <c r="G631" s="54">
+        <v>0</v>
+      </c>
+      <c r="H631" s="54">
+        <v>0</v>
+      </c>
+      <c r="I631" s="54">
+        <v>0</v>
+      </c>
+      <c r="J631" s="54">
+        <v>0</v>
+      </c>
+      <c r="K631" s="54">
+        <v>0</v>
+      </c>
+      <c r="L631" s="55">
+        <v>0</v>
+      </c>
+      <c r="M631" s="54">
+        <v>0</v>
+      </c>
+      <c r="N631" s="55">
+        <v>0</v>
+      </c>
+      <c r="O631" s="10">
+        <v>0</v>
+      </c>
+      <c r="P631" s="54"/>
+      <c r="Q631" s="56">
+        <f>+P631</f>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1">
         <v>333101</v>
       </c>
-      <c r="B627" s="52">
+      <c r="B632" s="52">
         <v>10101</v>
       </c>
-      <c r="C627" s="53" t="inlineStr">
+      <c r="C632" s="53" t="inlineStr">
         <is>
           <t>SAN PEDRO TOTOLAPA</t>
         </is>
       </c>
-      <c r="D627" s="57">
+      <c r="D632" s="57">
         <v>94</v>
       </c>
-      <c r="E627" s="57">
+      <c r="E632" s="57">
         <v>138</v>
       </c>
-      <c r="F627" s="10">
-        <f>E627*0.666*24/72</f>
-      </c>
-      <c r="G627" s="54">
-        <v>0</v>
-      </c>
-      <c r="H627" s="54">
-        <v>0</v>
-      </c>
-      <c r="I627" s="54">
-        <v>0</v>
-      </c>
-      <c r="J627" s="54">
-        <v>0</v>
-      </c>
-      <c r="K627" s="54">
-        <v>0</v>
-      </c>
-      <c r="L627" s="55">
-        <v>0</v>
-      </c>
-      <c r="M627" s="54">
-        <v>0</v>
-      </c>
-      <c r="N627" s="55">
-        <v>0</v>
-      </c>
-      <c r="O627" s="10">
-        <v>0</v>
-      </c>
-      <c r="P627" s="54"/>
-      <c r="Q627" s="56">
-        <f>+P627</f>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" s="1">
+      <c r="F632" s="10">
+        <f>E632*0.666*24/72</f>
+      </c>
+      <c r="G632" s="54">
+        <v>0</v>
+      </c>
+      <c r="H632" s="54">
+        <v>0</v>
+      </c>
+      <c r="I632" s="54">
+        <v>0</v>
+      </c>
+      <c r="J632" s="54">
+        <v>0</v>
+      </c>
+      <c r="K632" s="54">
+        <v>0</v>
+      </c>
+      <c r="L632" s="55">
+        <v>0</v>
+      </c>
+      <c r="M632" s="54">
+        <v>0</v>
+      </c>
+      <c r="N632" s="55">
+        <v>0</v>
+      </c>
+      <c r="O632" s="10">
+        <v>0</v>
+      </c>
+      <c r="P632" s="54"/>
+      <c r="Q632" s="56">
+        <f>+P632</f>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1">
         <v>338102</v>
       </c>
-      <c r="B628" s="52">
+      <c r="B633" s="52">
         <v>10101</v>
       </c>
-      <c r="C628" s="53" t="inlineStr">
+      <c r="C633" s="53" t="inlineStr">
         <is>
           <t>BARRIO ALTO</t>
         </is>
       </c>
-      <c r="D628" s="57">
+      <c r="D633" s="57">
         <v>58</v>
       </c>
-      <c r="E628" s="57">
+      <c r="E633" s="57">
         <v>123</v>
       </c>
-      <c r="F628" s="10">
-        <f>E628*0.666*24/72</f>
-      </c>
-      <c r="G628" s="54">
-        <v>0</v>
-      </c>
-      <c r="H628" s="54">
-        <v>0</v>
-      </c>
-      <c r="I628" s="54">
-        <v>0</v>
-      </c>
-      <c r="J628" s="54">
-        <v>0</v>
-      </c>
-      <c r="K628" s="54">
-        <v>0</v>
-      </c>
-      <c r="L628" s="55">
-        <v>0</v>
-      </c>
-      <c r="M628" s="54">
-        <v>0</v>
-      </c>
-      <c r="N628" s="55">
-        <v>0</v>
-      </c>
-      <c r="O628" s="10">
-        <v>0</v>
-      </c>
-      <c r="P628" s="54"/>
-      <c r="Q628" s="56">
-        <f>+P628</f>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" s="1">
+      <c r="F633" s="10">
+        <f>E633*0.666*24/72</f>
+      </c>
+      <c r="G633" s="54">
+        <v>0</v>
+      </c>
+      <c r="H633" s="54">
+        <v>0</v>
+      </c>
+      <c r="I633" s="54">
+        <v>0</v>
+      </c>
+      <c r="J633" s="54">
+        <v>0</v>
+      </c>
+      <c r="K633" s="54">
+        <v>0</v>
+      </c>
+      <c r="L633" s="55">
+        <v>0</v>
+      </c>
+      <c r="M633" s="54">
+        <v>0</v>
+      </c>
+      <c r="N633" s="55">
+        <v>0</v>
+      </c>
+      <c r="O633" s="10">
+        <v>0</v>
+      </c>
+      <c r="P633" s="54"/>
+      <c r="Q633" s="56">
+        <f>+P633</f>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1">
         <v>385117</v>
       </c>
-      <c r="B629" s="52">
+      <c r="B634" s="52">
         <v>10101</v>
       </c>
-      <c r="C629" s="53" t="inlineStr">
+      <c r="C634" s="53" t="inlineStr">
         <is>
           <t>COLONIA SANTA CRUZ XOXOCOTL N</t>
         </is>
       </c>
-      <c r="D629" s="57">
+      <c r="D634" s="57">
         <v>256</v>
       </c>
-      <c r="E629" s="57">
+      <c r="E634" s="57">
         <v>445</v>
       </c>
-      <c r="F629" s="10">
-        <f>E629*0.666*24/72</f>
-      </c>
-      <c r="G629" s="54">
-        <v>0</v>
-      </c>
-      <c r="H629" s="54">
-        <v>0</v>
-      </c>
-      <c r="I629" s="54">
-        <v>0</v>
-      </c>
-      <c r="J629" s="54">
-        <v>0</v>
-      </c>
-      <c r="K629" s="54">
-        <v>0</v>
-      </c>
-      <c r="L629" s="55">
-        <v>0</v>
-      </c>
-      <c r="M629" s="54">
-        <v>0</v>
-      </c>
-      <c r="N629" s="55">
-        <v>0</v>
-      </c>
-      <c r="O629" s="10">
-        <v>0</v>
-      </c>
-      <c r="P629" s="54"/>
-      <c r="Q629" s="56">
-        <f>+P629</f>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" s="1">
+      <c r="F634" s="10">
+        <f>E634*0.666*24/72</f>
+      </c>
+      <c r="G634" s="54">
+        <v>0</v>
+      </c>
+      <c r="H634" s="54">
+        <v>0</v>
+      </c>
+      <c r="I634" s="54">
+        <v>0</v>
+      </c>
+      <c r="J634" s="54">
+        <v>0</v>
+      </c>
+      <c r="K634" s="54">
+        <v>0</v>
+      </c>
+      <c r="L634" s="55">
+        <v>0</v>
+      </c>
+      <c r="M634" s="54">
+        <v>0</v>
+      </c>
+      <c r="N634" s="55">
+        <v>0</v>
+      </c>
+      <c r="O634" s="10">
+        <v>0</v>
+      </c>
+      <c r="P634" s="54"/>
+      <c r="Q634" s="56">
+        <f>+P634</f>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1">
         <v>405101</v>
       </c>
-      <c r="B630" s="52">
+      <c r="B635" s="52">
         <v>10101</v>
       </c>
-      <c r="C630" s="53" t="inlineStr">
+      <c r="C635" s="53" t="inlineStr">
         <is>
           <t>CENTRO CHILAPA DE DIAZ</t>
         </is>
       </c>
-      <c r="D630" s="57">
+      <c r="D635" s="57">
         <v>75</v>
       </c>
-      <c r="E630" s="57">
+      <c r="E635" s="57">
         <v>124</v>
       </c>
-      <c r="F630" s="10">
-        <f>E630*0.666*24/72</f>
-      </c>
-      <c r="G630" s="54">
-        <v>0</v>
-      </c>
-      <c r="H630" s="54">
-        <v>0</v>
-      </c>
-      <c r="I630" s="54">
-        <v>0</v>
-      </c>
-      <c r="J630" s="54">
-        <v>0</v>
-      </c>
-      <c r="K630" s="54">
-        <v>0</v>
-      </c>
-      <c r="L630" s="55">
-        <v>0</v>
-      </c>
-      <c r="M630" s="54">
-        <v>0</v>
-      </c>
-      <c r="N630" s="55">
-        <v>0</v>
-      </c>
-      <c r="O630" s="10">
-        <v>0</v>
-      </c>
-      <c r="P630" s="54"/>
-      <c r="Q630" s="56">
-        <f>+P630</f>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" s="1">
+      <c r="F635" s="10">
+        <f>E635*0.666*24/72</f>
+      </c>
+      <c r="G635" s="54">
+        <v>0</v>
+      </c>
+      <c r="H635" s="54">
+        <v>0</v>
+      </c>
+      <c r="I635" s="54">
+        <v>0</v>
+      </c>
+      <c r="J635" s="54">
+        <v>0</v>
+      </c>
+      <c r="K635" s="54">
+        <v>0</v>
+      </c>
+      <c r="L635" s="55">
+        <v>0</v>
+      </c>
+      <c r="M635" s="54">
+        <v>0</v>
+      </c>
+      <c r="N635" s="55">
+        <v>0</v>
+      </c>
+      <c r="O635" s="10">
+        <v>0</v>
+      </c>
+      <c r="P635" s="54"/>
+      <c r="Q635" s="56">
+        <f>+P635</f>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1">
         <v>421101</v>
       </c>
-      <c r="B631" s="52">
+      <c r="B636" s="52">
         <v>10101</v>
       </c>
-      <c r="C631" s="53" t="inlineStr">
+      <c r="C636" s="53" t="inlineStr">
         <is>
           <t>MIXTEQUILLA</t>
         </is>
       </c>
-      <c r="D631" s="57">
+      <c r="D636" s="57">
         <v>80</v>
       </c>
-      <c r="E631" s="57">
+      <c r="E636" s="57">
         <v>113</v>
       </c>
-      <c r="F631" s="10">
-        <f>E631*0.666*24/72</f>
-      </c>
-      <c r="G631" s="54">
-        <v>0</v>
-      </c>
-      <c r="H631" s="54">
-        <v>0</v>
-      </c>
-      <c r="I631" s="54">
-        <v>0</v>
-      </c>
-      <c r="J631" s="54">
-        <v>0</v>
-      </c>
-      <c r="K631" s="54">
-        <v>0</v>
-      </c>
-      <c r="L631" s="55">
-        <v>0</v>
-      </c>
-      <c r="M631" s="54">
-        <v>0</v>
-      </c>
-      <c r="N631" s="55">
-        <v>0</v>
-      </c>
-      <c r="O631" s="10">
-        <v>0</v>
-      </c>
-      <c r="P631" s="54"/>
-      <c r="Q631" s="56">
-        <f>+P631</f>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" s="1">
+      <c r="F636" s="10">
+        <f>E636*0.666*24/72</f>
+      </c>
+      <c r="G636" s="54">
+        <v>0</v>
+      </c>
+      <c r="H636" s="54">
+        <v>0</v>
+      </c>
+      <c r="I636" s="54">
+        <v>0</v>
+      </c>
+      <c r="J636" s="54">
+        <v>0</v>
+      </c>
+      <c r="K636" s="54">
+        <v>0</v>
+      </c>
+      <c r="L636" s="55">
+        <v>0</v>
+      </c>
+      <c r="M636" s="54">
+        <v>0</v>
+      </c>
+      <c r="N636" s="55">
+        <v>0</v>
+      </c>
+      <c r="O636" s="10">
+        <v>0</v>
+      </c>
+      <c r="P636" s="54"/>
+      <c r="Q636" s="56">
+        <f>+P636</f>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1">
         <v>427102</v>
       </c>
-      <c r="B632" s="52">
+      <c r="B637" s="52">
         <v>10101</v>
       </c>
-      <c r="C632" s="53" t="inlineStr">
+      <c r="C637" s="53" t="inlineStr">
         <is>
           <t>RINCON VIEJO</t>
         </is>
       </c>
-      <c r="D632" s="57">
+      <c r="D637" s="57">
         <v>250</v>
       </c>
-      <c r="E632" s="57">
+      <c r="E637" s="57">
         <v>425</v>
       </c>
-      <c r="F632" s="10">
-        <f>E632*0.666*24/72</f>
-      </c>
-      <c r="G632" s="54">
-        <v>0</v>
-      </c>
-      <c r="H632" s="54">
-        <v>0</v>
-      </c>
-      <c r="I632" s="54">
-        <v>0</v>
-      </c>
-      <c r="J632" s="54">
-        <v>0</v>
-      </c>
-      <c r="K632" s="54">
-        <v>0</v>
-      </c>
-      <c r="L632" s="55">
-        <v>0</v>
-      </c>
-      <c r="M632" s="54">
-        <v>0</v>
-      </c>
-      <c r="N632" s="55">
-        <v>0</v>
-      </c>
-      <c r="O632" s="10">
-        <v>0</v>
-      </c>
-      <c r="P632" s="54"/>
-      <c r="Q632" s="56">
-        <f>+P632</f>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" s="1">
+      <c r="F637" s="10">
+        <f>E637*0.666*24/72</f>
+      </c>
+      <c r="G637" s="54">
+        <v>0</v>
+      </c>
+      <c r="H637" s="54">
+        <v>0</v>
+      </c>
+      <c r="I637" s="54">
+        <v>0</v>
+      </c>
+      <c r="J637" s="54">
+        <v>0</v>
+      </c>
+      <c r="K637" s="54">
+        <v>0</v>
+      </c>
+      <c r="L637" s="55">
+        <v>0</v>
+      </c>
+      <c r="M637" s="54">
+        <v>0</v>
+      </c>
+      <c r="N637" s="55">
+        <v>0</v>
+      </c>
+      <c r="O637" s="10">
+        <v>0</v>
+      </c>
+      <c r="P637" s="54"/>
+      <c r="Q637" s="56">
+        <f>+P637</f>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1">
         <v>441101</v>
       </c>
-      <c r="B633" s="52">
+      <c r="B638" s="52">
         <v>10101</v>
       </c>
-      <c r="C633" s="53" t="inlineStr">
+      <c r="C638" s="53" t="inlineStr">
         <is>
           <t>SANTA MARIA XADANI</t>
         </is>
       </c>
-      <c r="D633" s="57">
+      <c r="D638" s="57">
         <v>286</v>
       </c>
-      <c r="E633" s="57">
+      <c r="E638" s="57">
         <v>427</v>
       </c>
-      <c r="F633" s="10">
-        <f>E633*0.666*24/72</f>
-      </c>
-      <c r="G633" s="54">
-        <v>0</v>
-      </c>
-      <c r="H633" s="54">
-        <v>0</v>
-      </c>
-      <c r="I633" s="54">
-        <v>0</v>
-      </c>
-      <c r="J633" s="54">
-        <v>0</v>
-      </c>
-      <c r="K633" s="54">
-        <v>0</v>
-      </c>
-      <c r="L633" s="55">
-        <v>0</v>
-      </c>
-      <c r="M633" s="54">
-        <v>0</v>
-      </c>
-      <c r="N633" s="55">
-        <v>0</v>
-      </c>
-      <c r="O633" s="10">
-        <v>0</v>
-      </c>
-      <c r="P633" s="54"/>
-      <c r="Q633" s="56">
-        <f>+P633</f>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" s="1">
+      <c r="F638" s="10">
+        <f>E638*0.666*24/72</f>
+      </c>
+      <c r="G638" s="54">
+        <v>0</v>
+      </c>
+      <c r="H638" s="54">
+        <v>0</v>
+      </c>
+      <c r="I638" s="54">
+        <v>0</v>
+      </c>
+      <c r="J638" s="54">
+        <v>0</v>
+      </c>
+      <c r="K638" s="54">
+        <v>0</v>
+      </c>
+      <c r="L638" s="55">
+        <v>0</v>
+      </c>
+      <c r="M638" s="54">
+        <v>0</v>
+      </c>
+      <c r="N638" s="55">
+        <v>0</v>
+      </c>
+      <c r="O638" s="10">
+        <v>0</v>
+      </c>
+      <c r="P638" s="54"/>
+      <c r="Q638" s="56">
+        <f>+P638</f>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1">
         <v>462102</v>
       </c>
-      <c r="B634" s="52">
+      <c r="B639" s="52">
         <v>10101</v>
       </c>
-      <c r="C634" s="53" t="inlineStr">
+      <c r="C639" s="53" t="inlineStr">
         <is>
           <t>SANTIAGO HUAJOLOTITLAN</t>
         </is>
       </c>
-      <c r="D634" s="57">
+      <c r="D639" s="57">
         <v>145</v>
       </c>
-      <c r="E634" s="57">
+      <c r="E639" s="57">
         <v>228</v>
       </c>
-      <c r="F634" s="10">
-        <f>E634*0.666*24/72</f>
-      </c>
-      <c r="G634" s="54">
-        <v>0</v>
-      </c>
-      <c r="H634" s="54">
-        <v>0</v>
-      </c>
-      <c r="I634" s="54">
-        <v>0</v>
-      </c>
-      <c r="J634" s="54">
-        <v>0</v>
-      </c>
-      <c r="K634" s="54">
-        <v>0</v>
-      </c>
-      <c r="L634" s="55">
-        <v>0</v>
-      </c>
-      <c r="M634" s="54">
-        <v>0</v>
-      </c>
-      <c r="N634" s="55">
-        <v>0</v>
-      </c>
-      <c r="O634" s="10">
-        <v>0</v>
-      </c>
-      <c r="P634" s="54"/>
-      <c r="Q634" s="56">
-        <f>+P634</f>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" s="1">
+      <c r="F639" s="10">
+        <f>E639*0.666*24/72</f>
+      </c>
+      <c r="G639" s="54">
+        <v>0</v>
+      </c>
+      <c r="H639" s="54">
+        <v>0</v>
+      </c>
+      <c r="I639" s="54">
+        <v>0</v>
+      </c>
+      <c r="J639" s="54">
+        <v>0</v>
+      </c>
+      <c r="K639" s="54">
+        <v>0</v>
+      </c>
+      <c r="L639" s="55">
+        <v>0</v>
+      </c>
+      <c r="M639" s="54">
+        <v>0</v>
+      </c>
+      <c r="N639" s="55">
+        <v>0</v>
+      </c>
+      <c r="O639" s="10">
+        <v>0</v>
+      </c>
+      <c r="P639" s="54"/>
+      <c r="Q639" s="56">
+        <f>+P639</f>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1">
         <v>486102</v>
       </c>
-      <c r="B635" s="52">
+      <c r="B640" s="52">
         <v>10101</v>
       </c>
-      <c r="C635" s="53" t="inlineStr">
+      <c r="C640" s="53" t="inlineStr">
         <is>
           <t>VILLA TEJUPAM DE LA UNION</t>
         </is>
       </c>
-      <c r="D635" s="57">
+      <c r="D640" s="57">
         <v>49</v>
       </c>
-      <c r="E635" s="57">
+      <c r="E640" s="57">
         <v>83</v>
       </c>
-      <c r="F635" s="10">
-        <f>E635*0.666*24/72</f>
-      </c>
-      <c r="G635" s="54">
-        <v>0</v>
-      </c>
-      <c r="H635" s="54">
-        <v>0</v>
-      </c>
-      <c r="I635" s="54">
-        <v>0</v>
-      </c>
-      <c r="J635" s="54">
-        <v>0</v>
-      </c>
-      <c r="K635" s="54">
-        <v>0</v>
-      </c>
-      <c r="L635" s="55">
-        <v>0</v>
-      </c>
-      <c r="M635" s="54">
-        <v>0</v>
-      </c>
-      <c r="N635" s="55">
-        <v>0</v>
-      </c>
-      <c r="O635" s="10">
-        <v>0</v>
-      </c>
-      <c r="P635" s="54"/>
-      <c r="Q635" s="56">
-        <f>+P635</f>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" s="1">
+      <c r="F640" s="10">
+        <f>E640*0.666*24/72</f>
+      </c>
+      <c r="G640" s="54">
+        <v>0</v>
+      </c>
+      <c r="H640" s="54">
+        <v>0</v>
+      </c>
+      <c r="I640" s="54">
+        <v>0</v>
+      </c>
+      <c r="J640" s="54">
+        <v>0</v>
+      </c>
+      <c r="K640" s="54">
+        <v>0</v>
+      </c>
+      <c r="L640" s="55">
+        <v>0</v>
+      </c>
+      <c r="M640" s="54">
+        <v>0</v>
+      </c>
+      <c r="N640" s="55">
+        <v>0</v>
+      </c>
+      <c r="O640" s="10">
+        <v>0</v>
+      </c>
+      <c r="P640" s="54"/>
+      <c r="Q640" s="56">
+        <f>+P640</f>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1">
         <v>515104</v>
       </c>
-      <c r="B636" s="52">
+      <c r="B641" s="52">
         <v>10101</v>
       </c>
-      <c r="C636" s="53" t="inlineStr">
+      <c r="C641" s="53" t="inlineStr">
         <is>
           <t>BARRIO  SANTA MARIA</t>
         </is>
       </c>
-      <c r="D636" s="57">
+      <c r="D641" s="57">
         <v>104</v>
       </c>
-      <c r="E636" s="57">
+      <c r="E641" s="57">
         <v>183</v>
       </c>
-      <c r="F636" s="10">
-        <f>E636*0.666*24/72</f>
-      </c>
-      <c r="G636" s="54">
-        <v>0</v>
-      </c>
-      <c r="H636" s="54">
-        <v>0</v>
-      </c>
-      <c r="I636" s="54">
-        <v>0</v>
-      </c>
-      <c r="J636" s="54">
-        <v>0</v>
-      </c>
-      <c r="K636" s="54">
-        <v>0</v>
-      </c>
-      <c r="L636" s="55">
-        <v>0</v>
-      </c>
-      <c r="M636" s="54">
-        <v>0</v>
-      </c>
-      <c r="N636" s="55">
-        <v>0</v>
-      </c>
-      <c r="O636" s="10">
-        <v>0</v>
-      </c>
-      <c r="P636" s="54"/>
-      <c r="Q636" s="56">
-        <f>+P636</f>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" s="1">
+      <c r="F641" s="10">
+        <f>E641*0.666*24/72</f>
+      </c>
+      <c r="G641" s="54">
+        <v>0</v>
+      </c>
+      <c r="H641" s="54">
+        <v>0</v>
+      </c>
+      <c r="I641" s="54">
+        <v>0</v>
+      </c>
+      <c r="J641" s="54">
+        <v>0</v>
+      </c>
+      <c r="K641" s="54">
+        <v>0</v>
+      </c>
+      <c r="L641" s="55">
+        <v>0</v>
+      </c>
+      <c r="M641" s="54">
+        <v>0</v>
+      </c>
+      <c r="N641" s="55">
+        <v>0</v>
+      </c>
+      <c r="O641" s="10">
+        <v>0</v>
+      </c>
+      <c r="P641" s="54"/>
+      <c r="Q641" s="56">
+        <f>+P641</f>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1">
         <v>547101</v>
       </c>
-      <c r="B637" s="52">
+      <c r="B642" s="52">
         <v>10101</v>
       </c>
-      <c r="C637" s="53" t="inlineStr">
+      <c r="C642" s="53" t="inlineStr">
         <is>
           <t>TEOTONGO</t>
         </is>
       </c>
-      <c r="D637" s="57">
+      <c r="D642" s="57">
         <v>74</v>
       </c>
-      <c r="E637" s="57">
+      <c r="E642" s="57">
         <v>129</v>
       </c>
-      <c r="F637" s="10">
-        <f>E637*0.666*24/72</f>
-      </c>
-      <c r="G637" s="54">
-        <v>0</v>
-      </c>
-      <c r="H637" s="54">
-        <v>0</v>
-      </c>
-      <c r="I637" s="54">
-        <v>0</v>
-      </c>
-      <c r="J637" s="54">
-        <v>0</v>
-      </c>
-      <c r="K637" s="54">
-        <v>0</v>
-      </c>
-      <c r="L637" s="55">
-        <v>0</v>
-      </c>
-      <c r="M637" s="54">
-        <v>0</v>
-      </c>
-      <c r="N637" s="55">
-        <v>0</v>
-      </c>
-      <c r="O637" s="10">
-        <v>0</v>
-      </c>
-      <c r="P637" s="54"/>
-      <c r="Q637" s="56">
-        <f>+P637</f>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" s="1">
+      <c r="F642" s="10">
+        <f>E642*0.666*24/72</f>
+      </c>
+      <c r="G642" s="54">
+        <v>0</v>
+      </c>
+      <c r="H642" s="54">
+        <v>0</v>
+      </c>
+      <c r="I642" s="54">
+        <v>0</v>
+      </c>
+      <c r="J642" s="54">
+        <v>0</v>
+      </c>
+      <c r="K642" s="54">
+        <v>0</v>
+      </c>
+      <c r="L642" s="55">
+        <v>0</v>
+      </c>
+      <c r="M642" s="54">
+        <v>0</v>
+      </c>
+      <c r="N642" s="55">
+        <v>0</v>
+      </c>
+      <c r="O642" s="10">
+        <v>0</v>
+      </c>
+      <c r="P642" s="54"/>
+      <c r="Q642" s="56">
+        <f>+P642</f>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1">
         <v>551103</v>
       </c>
-      <c r="B638" s="52">
+      <c r="B643" s="52">
         <v>10101</v>
       </c>
-      <c r="C638" s="53" t="inlineStr">
+      <c r="C643" s="53" t="inlineStr">
         <is>
           <t>FRACCONAMIENTO CIUDAD YAGUL</t>
         </is>
       </c>
-      <c r="D638" s="57">
+      <c r="D643" s="57">
         <v>130</v>
       </c>
-      <c r="E638" s="57">
+      <c r="E643" s="57">
         <v>219</v>
       </c>
-      <c r="F638" s="10">
-        <f>E638*0.666*24/72</f>
-      </c>
-      <c r="G638" s="54">
-        <v>0</v>
-      </c>
-      <c r="H638" s="54">
-        <v>0</v>
-      </c>
-      <c r="I638" s="54">
-        <v>0</v>
-      </c>
-      <c r="J638" s="54">
-        <v>0</v>
-      </c>
-      <c r="K638" s="54">
-        <v>0</v>
-      </c>
-      <c r="L638" s="55">
-        <v>0</v>
-      </c>
-      <c r="M638" s="54">
-        <v>0</v>
-      </c>
-      <c r="N638" s="55">
-        <v>0</v>
-      </c>
-      <c r="O638" s="10">
-        <v>0</v>
-      </c>
-      <c r="P638" s="54"/>
-      <c r="Q638" s="56">
-        <f>+P638</f>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" s="1">
+      <c r="F643" s="10">
+        <f>E643*0.666*24/72</f>
+      </c>
+      <c r="G643" s="54">
+        <v>0</v>
+      </c>
+      <c r="H643" s="54">
+        <v>0</v>
+      </c>
+      <c r="I643" s="54">
+        <v>0</v>
+      </c>
+      <c r="J643" s="54">
+        <v>0</v>
+      </c>
+      <c r="K643" s="54">
+        <v>0</v>
+      </c>
+      <c r="L643" s="55">
+        <v>0</v>
+      </c>
+      <c r="M643" s="54">
+        <v>0</v>
+      </c>
+      <c r="N643" s="55">
+        <v>0</v>
+      </c>
+      <c r="O643" s="10">
+        <v>0</v>
+      </c>
+      <c r="P643" s="54"/>
+      <c r="Q643" s="56">
+        <f>+P643</f>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1">
         <v>551105</v>
       </c>
-      <c r="B639" s="52">
+      <c r="B644" s="52">
         <v>10101</v>
       </c>
-      <c r="C639" s="53" t="inlineStr">
+      <c r="C644" s="53" t="inlineStr">
         <is>
           <t>RANCHO VALLE DEL LAGO</t>
         </is>
       </c>
-      <c r="D639" s="57">
+      <c r="D644" s="57">
         <v>80</v>
       </c>
-      <c r="E639" s="57">
+      <c r="E644" s="57">
         <v>145</v>
       </c>
-      <c r="F639" s="10">
-        <f>E639*0.666*24/72</f>
-      </c>
-      <c r="G639" s="54">
-        <v>0</v>
-      </c>
-      <c r="H639" s="54">
-        <v>0</v>
-      </c>
-      <c r="I639" s="54">
-        <v>0</v>
-      </c>
-      <c r="J639" s="54">
-        <v>0</v>
-      </c>
-      <c r="K639" s="54">
-        <v>0</v>
-      </c>
-      <c r="L639" s="55">
-        <v>0</v>
-      </c>
-      <c r="M639" s="54">
-        <v>0</v>
-      </c>
-      <c r="N639" s="55">
-        <v>0</v>
-      </c>
-      <c r="O639" s="10">
-        <v>0</v>
-      </c>
-      <c r="P639" s="54"/>
-      <c r="Q639" s="56">
-        <f>+P639</f>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" s="1">
+      <c r="F644" s="10">
+        <f>E644*0.666*24/72</f>
+      </c>
+      <c r="G644" s="54">
+        <v>0</v>
+      </c>
+      <c r="H644" s="54">
+        <v>0</v>
+      </c>
+      <c r="I644" s="54">
+        <v>0</v>
+      </c>
+      <c r="J644" s="54">
+        <v>0</v>
+      </c>
+      <c r="K644" s="54">
+        <v>0</v>
+      </c>
+      <c r="L644" s="55">
+        <v>0</v>
+      </c>
+      <c r="M644" s="54">
+        <v>0</v>
+      </c>
+      <c r="N644" s="55">
+        <v>0</v>
+      </c>
+      <c r="O644" s="10">
+        <v>0</v>
+      </c>
+      <c r="P644" s="54"/>
+      <c r="Q644" s="56">
+        <f>+P644</f>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1">
         <v>565111</v>
       </c>
-      <c r="B640" s="52">
+      <c r="B645" s="52">
         <v>10101</v>
       </c>
-      <c r="C640" s="53" t="inlineStr">
+      <c r="C645" s="53" t="inlineStr">
         <is>
           <t>CAMPO REAL</t>
         </is>
       </c>
-      <c r="D640" s="57">
+      <c r="D645" s="57">
         <v>52</v>
       </c>
-      <c r="E640" s="57">
+      <c r="E645" s="57">
         <v>99</v>
       </c>
-      <c r="F640" s="10">
-        <f>E640*0.666*24/72</f>
-      </c>
-      <c r="G640" s="54">
-        <v>0</v>
-      </c>
-      <c r="H640" s="54">
-        <v>0</v>
-      </c>
-      <c r="I640" s="54">
-        <v>0</v>
-      </c>
-      <c r="J640" s="54">
-        <v>0</v>
-      </c>
-      <c r="K640" s="54">
-        <v>0</v>
-      </c>
-      <c r="L640" s="55">
-        <v>0</v>
-      </c>
-      <c r="M640" s="54">
-        <v>0</v>
-      </c>
-      <c r="N640" s="55">
-        <v>0</v>
-      </c>
-      <c r="O640" s="10">
-        <v>0</v>
-      </c>
-      <c r="P640" s="54"/>
-      <c r="Q640" s="56">
-        <f>+P640</f>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" s="1">
+      <c r="F645" s="10">
+        <f>E645*0.666*24/72</f>
+      </c>
+      <c r="G645" s="54">
+        <v>0</v>
+      </c>
+      <c r="H645" s="54">
+        <v>0</v>
+      </c>
+      <c r="I645" s="54">
+        <v>0</v>
+      </c>
+      <c r="J645" s="54">
+        <v>0</v>
+      </c>
+      <c r="K645" s="54">
+        <v>0</v>
+      </c>
+      <c r="L645" s="55">
+        <v>0</v>
+      </c>
+      <c r="M645" s="54">
+        <v>0</v>
+      </c>
+      <c r="N645" s="55">
+        <v>0</v>
+      </c>
+      <c r="O645" s="10">
+        <v>0</v>
+      </c>
+      <c r="P645" s="54"/>
+      <c r="Q645" s="56">
+        <f>+P645</f>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1">
         <v>570104</v>
       </c>
-      <c r="B641" s="52">
+      <c r="B646" s="52">
         <v>10101</v>
       </c>
-      <c r="C641" s="53" t="inlineStr">
+      <c r="C646" s="53" t="inlineStr">
         <is>
           <t>ZIMATLAN DE ALVAREZ</t>
         </is>
       </c>
-      <c r="D641" s="57">
+      <c r="D646" s="57">
         <v>171</v>
       </c>
-      <c r="E641" s="57">
+      <c r="E646" s="57">
         <v>290</v>
       </c>
-      <c r="F641" s="10">
-        <f>E641*0.666*24/72</f>
-      </c>
-      <c r="G641" s="54">
-        <v>0</v>
-      </c>
-      <c r="H641" s="54">
-        <v>0</v>
-      </c>
-      <c r="I641" s="54">
-        <v>0</v>
-      </c>
-      <c r="J641" s="54">
-        <v>0</v>
-      </c>
-      <c r="K641" s="54">
-        <v>0</v>
-      </c>
-      <c r="L641" s="55">
-        <v>0</v>
-      </c>
-      <c r="M641" s="54">
-        <v>0</v>
-      </c>
-      <c r="N641" s="55">
-        <v>0</v>
-      </c>
-      <c r="O641" s="10">
-        <v>0</v>
-      </c>
-      <c r="P641" s="54"/>
-      <c r="Q641" s="56">
-        <f>+P641</f>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" s="1">
+      <c r="F646" s="10">
+        <f>E646*0.666*24/72</f>
+      </c>
+      <c r="G646" s="54">
+        <v>0</v>
+      </c>
+      <c r="H646" s="54">
+        <v>0</v>
+      </c>
+      <c r="I646" s="54">
+        <v>0</v>
+      </c>
+      <c r="J646" s="54">
+        <v>0</v>
+      </c>
+      <c r="K646" s="54">
+        <v>0</v>
+      </c>
+      <c r="L646" s="55">
+        <v>0</v>
+      </c>
+      <c r="M646" s="54">
+        <v>0</v>
+      </c>
+      <c r="N646" s="55">
+        <v>0</v>
+      </c>
+      <c r="O646" s="10">
+        <v>0</v>
+      </c>
+      <c r="P646" s="54"/>
+      <c r="Q646" s="56">
+        <f>+P646</f>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1">
         <v>710374</v>
       </c>
-      <c r="B642" s="52">
+      <c r="B647" s="52">
         <v>10101</v>
       </c>
-      <c r="C642" s="53" t="inlineStr">
+      <c r="C647" s="53" t="inlineStr">
         <is>
           <t>MATIAS ROMERO  BARRIO NUEVO</t>
         </is>
       </c>
-      <c r="D642" s="57">
+      <c r="D647" s="57">
         <v>70</v>
       </c>
-      <c r="E642" s="57">
+      <c r="E647" s="57">
         <v>90</v>
       </c>
-      <c r="F642" s="10">
-        <f>E642*0.666*24/72</f>
-      </c>
-      <c r="G642" s="54">
-        <v>0</v>
-      </c>
-      <c r="H642" s="54">
-        <v>0</v>
-      </c>
-      <c r="I642" s="54">
-        <v>0</v>
-      </c>
-      <c r="J642" s="54">
-        <v>0</v>
-      </c>
-      <c r="K642" s="54">
-        <v>0</v>
-      </c>
-      <c r="L642" s="55">
-        <v>0</v>
-      </c>
-      <c r="M642" s="54">
-        <v>0</v>
-      </c>
-      <c r="N642" s="55">
-        <v>0</v>
-      </c>
-      <c r="O642" s="10">
-        <v>0</v>
-      </c>
-      <c r="P642" s="54"/>
-      <c r="Q642" s="56">
-        <f>+P642</f>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" s="43" t="inlineStr">
+      <c r="F647" s="10">
+        <f>E647*0.666*24/72</f>
+      </c>
+      <c r="G647" s="54">
+        <v>0</v>
+      </c>
+      <c r="H647" s="54">
+        <v>0</v>
+      </c>
+      <c r="I647" s="54">
+        <v>0</v>
+      </c>
+      <c r="J647" s="54">
+        <v>0</v>
+      </c>
+      <c r="K647" s="54">
+        <v>0</v>
+      </c>
+      <c r="L647" s="55">
+        <v>0</v>
+      </c>
+      <c r="M647" s="54">
+        <v>0</v>
+      </c>
+      <c r="N647" s="55">
+        <v>0</v>
+      </c>
+      <c r="O647" s="10">
+        <v>0</v>
+      </c>
+      <c r="P647" s="54"/>
+      <c r="Q647" s="56">
+        <f>+P647</f>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="43" t="inlineStr">
         <is>
           <t>T O T A L</t>
         </is>
       </c>
-      <c r="B644" s="44"/>
-      <c r="C644" s="45">
-        <f>COUNTA(A559:A642)</f>
-      </c>
-      <c r="D644" s="65">
-        <f>SUM(D559:D642)</f>
-      </c>
-      <c r="E644" s="65">
-        <f>SUM(E559:E642)</f>
-      </c>
-      <c r="F644" s="65">
-        <f>SUM(F559:F642)</f>
-      </c>
-      <c r="G644" s="65">
-        <f>SUM(G559:G642)</f>
-      </c>
-      <c r="H644" s="65">
-        <f>SUM(H559:H642)</f>
-      </c>
-      <c r="I644" s="65">
-        <f>SUM(I559:I642)</f>
-      </c>
-      <c r="J644" s="65">
-        <f>SUM(J559:J642)</f>
-      </c>
-      <c r="K644" s="65">
-        <f>SUM(K559:K642)</f>
-      </c>
-      <c r="L644" s="65">
-        <f>SUM(L559:L642)</f>
-      </c>
-      <c r="M644" s="65">
-        <f>SUM(M559:M642)</f>
-      </c>
-      <c r="N644" s="65">
-        <f>SUM(N559:N642)</f>
-      </c>
-      <c r="O644" s="65">
-        <f>SUM(O559:O642)</f>
-      </c>
-      <c r="P644" s="65">
-        <f>SUM(P559:P642)</f>
-      </c>
-      <c r="Q644" s="65">
-        <f>SUM(Q559:Q642)</f>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" s="66" t="inlineStr">
+      <c r="B649" s="44"/>
+      <c r="C649" s="45">
+        <f>COUNTA(A564:A647)</f>
+      </c>
+      <c r="D649" s="65">
+        <f>SUM(D564:D647)</f>
+      </c>
+      <c r="E649" s="65">
+        <f>SUM(E564:E647)</f>
+      </c>
+      <c r="F649" s="65">
+        <f>SUM(F564:F647)</f>
+      </c>
+      <c r="G649" s="65">
+        <f>SUM(G564:G647)</f>
+      </c>
+      <c r="H649" s="65">
+        <f>SUM(H564:H647)</f>
+      </c>
+      <c r="I649" s="65">
+        <f>SUM(I564:I647)</f>
+      </c>
+      <c r="J649" s="65">
+        <f>SUM(J564:J647)</f>
+      </c>
+      <c r="K649" s="65">
+        <f>SUM(K564:K647)</f>
+      </c>
+      <c r="L649" s="65">
+        <f>SUM(L564:L647)</f>
+      </c>
+      <c r="M649" s="65">
+        <f>SUM(M564:M647)</f>
+      </c>
+      <c r="N649" s="65">
+        <f>SUM(N564:N647)</f>
+      </c>
+      <c r="O649" s="65">
+        <f>SUM(O564:O647)</f>
+      </c>
+      <c r="P649" s="65">
+        <f>SUM(P564:P647)</f>
+      </c>
+      <c r="Q649" s="65">
+        <f>SUM(Q564:Q647)</f>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="66" t="inlineStr">
         <is>
           <t>OBSERVACIONES: </t>
         </is>
       </c>
-      <c r="B645" s="67"/>
-      <c r="C645" s="68"/>
-      <c r="D645" s="69"/>
-      <c r="E645" s="69"/>
-      <c r="F645" s="70"/>
-      <c r="G645" s="69"/>
-      <c r="H645" s="69"/>
-      <c r="I645" s="69"/>
-      <c r="J645" s="69"/>
-      <c r="K645" s="69"/>
-      <c r="L645" s="70"/>
-      <c r="M645" s="71"/>
-      <c r="N645" s="72"/>
-      <c r="O645" s="72"/>
-      <c r="P645" s="73"/>
-      <c r="Q645" s="74"/>
-    </row>
-    <row r="646">
-      <c r="P646" s="65" t="inlineStr">
+      <c r="B650" s="67"/>
+      <c r="C650" s="68"/>
+      <c r="D650" s="69"/>
+      <c r="E650" s="69"/>
+      <c r="F650" s="70"/>
+      <c r="G650" s="69"/>
+      <c r="H650" s="69"/>
+      <c r="I650" s="69"/>
+      <c r="J650" s="69"/>
+      <c r="K650" s="69"/>
+      <c r="L650" s="70"/>
+      <c r="M650" s="71"/>
+      <c r="N650" s="72"/>
+      <c r="O650" s="72"/>
+      <c r="P650" s="73"/>
+      <c r="Q650" s="74"/>
+    </row>
+    <row r="651">
+      <c r="P651" s="65" t="inlineStr">
         <is>
           <t>TOTAL A RECIBIR EN ALMACEN:</t>
         </is>
       </c>
-      <c r="Q646" s="65">
-        <f>Q644</f>
+      <c r="Q651" s="65">
+        <f>Q649</f>
       </c>
     </row>
   </sheetData>
@@ -72536,22 +72791,22 @@
         </is>
       </c>
       <c r="C52" s="1">
-        <f>+'POR ALMACEN'!C551</f>
+        <f>+'POR ALMACEN'!C556</f>
       </c>
       <c r="D52" s="1">
-        <f>+'POR ALMACEN'!D551</f>
+        <f>+'POR ALMACEN'!D556</f>
       </c>
       <c r="E52" s="1">
-        <f>+'POR ALMACEN'!E551</f>
+        <f>+'POR ALMACEN'!E556</f>
       </c>
       <c r="F52" s="1">
-        <f>+'POR ALMACEN'!F551</f>
+        <f>+'POR ALMACEN'!F556</f>
       </c>
       <c r="G52" s="1">
         <v>0</v>
       </c>
       <c r="H52" s="1">
-        <f>+'POR ALMACEN'!P551</f>
+        <f>+'POR ALMACEN'!P556</f>
       </c>
       <c r="I52" s="1">
         <f>H52-G52</f>
@@ -72564,22 +72819,22 @@
         </is>
       </c>
       <c r="C53" s="1">
-        <f>+'POR ALMACEN'!C644</f>
+        <f>+'POR ALMACEN'!C649</f>
       </c>
       <c r="D53" s="1">
-        <f>+'POR ALMACEN'!D644</f>
+        <f>+'POR ALMACEN'!D649</f>
       </c>
       <c r="E53" s="1">
-        <f>+'POR ALMACEN'!E644</f>
+        <f>+'POR ALMACEN'!E649</f>
       </c>
       <c r="F53" s="1">
-        <f>+'POR ALMACEN'!F644</f>
+        <f>+'POR ALMACEN'!F649</f>
       </c>
       <c r="G53" s="1">
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <f>+'POR ALMACEN'!P644</f>
+        <f>+'POR ALMACEN'!P649</f>
       </c>
       <c r="I53" s="1">
         <f>H53-G53</f>
